--- a/서버정보/20260601_리소스배포_운영.xlsx
+++ b/서버정보/20260601_리소스배포_운영.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{500DFDFB-1CDA-43DB-A62B-E7DFD691FF9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19F06432-2B1D-43FD-B1A1-DDBA604FBB39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12342,9 +12342,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
-    <tabColor rgb="FF00B050"/>
-  </sheetPr>
   <dimension ref="A1:AF73"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -18748,9 +18745,6 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52F281E7-0665-4BB7-80DB-4208A01A998B}">
-  <sheetPr>
-    <tabColor rgb="FF00B050"/>
-  </sheetPr>
   <dimension ref="A1:R73"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -22787,9 +22781,6 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAB1F184-7BFC-47CB-AC71-63C76B7E3D12}">
-  <sheetPr>
-    <tabColor rgb="FF00B050"/>
-  </sheetPr>
   <dimension ref="A1:M91"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -27520,9 +27511,6 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5444DC07-76A1-42D8-823C-45359A57A751}">
-  <sheetPr>
-    <tabColor rgb="FF00B050"/>
-  </sheetPr>
   <dimension ref="A1:J40"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -34344,9 +34332,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -34494,26 +34485,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -34537,9 +34517,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260601_리소스배포_운영.xlsx
+++ b/서버정보/20260601_리소스배포_운영.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19F06432-2B1D-43FD-B1A1-DDBA604FBB39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E50ED03-853B-4DFE-A5D5-1C61750B40F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -1659,7 +1659,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4770" uniqueCount="667">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4517" uniqueCount="662">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3695,22 +3695,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Linux</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>D8s_v5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10.155.161.68</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10.155.161.69</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>l-mon-ap-sbn</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3744,14 +3728,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>TEMP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ap</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>hazr-l-mon-whtap03</t>
   </si>
   <si>
@@ -3759,10 +3735,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10.155.161.70</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>l-mon-whtap03-nic</t>
   </si>
   <si>
@@ -4054,6 +4026,14 @@
   </si>
   <si>
     <t>hazr-p-puls-rg</t>
+  </si>
+  <si>
+    <t>hazr-p-dch-rg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-p-dch-des</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4557,7 +4537,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4879,15 +4859,6 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -4909,6 +4880,35 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom style="thin">
+          <color theme="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -5789,37 +5789,6 @@
     </dxf>
     <dxf>
       <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -5929,46 +5898,46 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="B1:AF73" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32">
-  <autoFilter ref="B1:AF73" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="B1:AF70" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32">
+  <autoFilter ref="B1:AF70" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="31">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Stage" dataDxfId="31"/>
     <tableColumn id="2" xr3:uid="{DD2076C4-D866-4329-BEA8-1D816DAF3627}" name="Role" dataDxfId="30">
       <calculatedColumnFormula array="1">UPPER(INDEX(_xlfn.TEXTSPLIT($D2, "-"), 3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="RGname" dataDxfId="29"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Location" dataDxfId="28"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name" dataDxfId="27"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="PrivateIP" dataDxfId="26"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="VmSize" dataDxfId="25"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="CPU" dataDxfId="24"/>
-    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="RAM" dataDxfId="23"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="AdminUsername" dataDxfId="22"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="AdminPassword" dataDxfId="21"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="OsType" dataDxfId="20"/>
-    <tableColumn id="10" xr3:uid="{5C5FDBAD-A0A4-4C75-968A-8587646674EE}" name="ImageResourceId" dataDxfId="19"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="OsDiskName" dataDxfId="18">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="RGname" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Location" dataDxfId="29"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name" dataDxfId="28"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="PrivateIP" dataDxfId="27"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="VmSize" dataDxfId="26"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="CPU" dataDxfId="25"/>
+    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="RAM" dataDxfId="24"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="AdminUsername" dataDxfId="23"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="AdminPassword" dataDxfId="22"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="OsType" dataDxfId="21"/>
+    <tableColumn id="10" xr3:uid="{5C5FDBAD-A0A4-4C75-968A-8587646674EE}" name="ImageResourceId" dataDxfId="20"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="OsDiskName" dataDxfId="19">
       <calculatedColumnFormula>SUBSTITUTE(F2,"hazr-","")&amp;"-osdisk"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="OsDiskSize" dataDxfId="17"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="OsDiskStorageType" dataDxfId="16"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="DataDiskName" dataDxfId="15"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="DataDiskSize" dataDxfId="14"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="DataDiskStorageType" dataDxfId="13"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="NicName" dataDxfId="12">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="OsDiskSize" dataDxfId="18"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="OsDiskStorageType" dataDxfId="17"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="DataDiskName" dataDxfId="16"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="DataDiskSize" dataDxfId="15"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="DataDiskStorageType" dataDxfId="14"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="NicName" dataDxfId="13">
       <calculatedColumnFormula>SUBSTITUTE(F2,"hazr-","")&amp;"-nic"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{6FD9A0A6-7008-49AB-B2C9-4BEDF1811434}" name="EnableAcceleratedNetworking" dataDxfId="11"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="IsStatic" dataDxfId="10"/>
-    <tableColumn id="11" xr3:uid="{65903CF2-1AF4-4B86-A9E4-474DE495E3CB}" name="VnetRG" dataDxfId="9"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="VnetName" dataDxfId="8"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="SubnetName" dataDxfId="7"/>
-    <tableColumn id="28" xr3:uid="{73185387-6B41-497F-9EB6-5675CC43B3E3}" name="UseOsDiskDoubleEncryption " dataDxfId="6"/>
-    <tableColumn id="21" xr3:uid="{804782E7-599A-496A-B10D-EFCB52F3E7DB}" name="DESRG" dataDxfId="5"/>
-    <tableColumn id="16" xr3:uid="{1ED2A695-2028-4644-8B0B-7B32A8F548C4}" name="DESName" dataDxfId="4"/>
-    <tableColumn id="36" xr3:uid="{9EB3DACA-84E4-4D05-8E76-433A4A9E33E7}" name="Zones" dataDxfId="3"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="SubscriptionName" dataDxfId="2"/>
-    <tableColumn id="35" xr3:uid="{A2E4758D-942B-4C99-96CE-9F1494B6961B}" name="Description" dataDxfId="1"/>
+    <tableColumn id="27" xr3:uid="{6FD9A0A6-7008-49AB-B2C9-4BEDF1811434}" name="EnableAcceleratedNetworking" dataDxfId="12"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="IsStatic" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{65903CF2-1AF4-4B86-A9E4-474DE495E3CB}" name="VnetRG" dataDxfId="10"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="VnetName" dataDxfId="9"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="SubnetName" dataDxfId="8"/>
+    <tableColumn id="28" xr3:uid="{73185387-6B41-497F-9EB6-5675CC43B3E3}" name="UseOsDiskDoubleEncryption " dataDxfId="7"/>
+    <tableColumn id="21" xr3:uid="{804782E7-599A-496A-B10D-EFCB52F3E7DB}" name="DESRG" dataDxfId="6"/>
+    <tableColumn id="16" xr3:uid="{1ED2A695-2028-4644-8B0B-7B32A8F548C4}" name="DESName" dataDxfId="5"/>
+    <tableColumn id="36" xr3:uid="{9EB3DACA-84E4-4D05-8E76-433A4A9E33E7}" name="Zones" dataDxfId="4"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="SubscriptionName" dataDxfId="3"/>
+    <tableColumn id="35" xr3:uid="{A2E4758D-942B-4C99-96CE-9F1494B6961B}" name="Description" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6538,72 +6507,72 @@
         <v>DCH</v>
       </c>
       <c r="D2" s="50" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="E2" s="50" t="s">
         <v>24</v>
       </c>
       <c r="F2" s="50" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
       <c r="G2" s="50" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="H2" s="50"/>
       <c r="I2" s="50"/>
       <c r="J2" s="50" t="s">
+        <v>576</v>
+      </c>
+      <c r="K2" s="50" t="s">
+        <v>613</v>
+      </c>
+      <c r="L2" s="50" t="s">
+        <v>577</v>
+      </c>
+      <c r="M2" s="50" t="s">
+        <v>614</v>
+      </c>
+      <c r="N2" s="50" t="s">
+        <v>578</v>
+      </c>
+      <c r="O2" s="50" t="s">
+        <v>615</v>
+      </c>
+      <c r="P2" s="50" t="s">
+        <v>579</v>
+      </c>
+      <c r="Q2" s="50" t="s">
+        <v>616</v>
+      </c>
+      <c r="R2" s="50" t="s">
+        <v>580</v>
+      </c>
+      <c r="S2" s="50" t="s">
+        <v>617</v>
+      </c>
+      <c r="T2" s="50" t="s">
+        <v>581</v>
+      </c>
+      <c r="U2" s="50" t="s">
+        <v>618</v>
+      </c>
+      <c r="V2" s="50" t="s">
+        <v>582</v>
+      </c>
+      <c r="W2" s="50" t="s">
+        <v>619</v>
+      </c>
+      <c r="X2" s="50" t="s">
         <v>583</v>
       </c>
-      <c r="K2" s="50" t="s">
+      <c r="Y2" s="50" t="s">
         <v>620</v>
       </c>
-      <c r="L2" s="50" t="s">
+      <c r="Z2" s="50" t="s">
         <v>584</v>
       </c>
-      <c r="M2" s="50" t="s">
+      <c r="AA2" s="50" t="s">
         <v>621</v>
-      </c>
-      <c r="N2" s="50" t="s">
-        <v>585</v>
-      </c>
-      <c r="O2" s="50" t="s">
-        <v>622</v>
-      </c>
-      <c r="P2" s="50" t="s">
-        <v>586</v>
-      </c>
-      <c r="Q2" s="50" t="s">
-        <v>623</v>
-      </c>
-      <c r="R2" s="50" t="s">
-        <v>587</v>
-      </c>
-      <c r="S2" s="50" t="s">
-        <v>624</v>
-      </c>
-      <c r="T2" s="50" t="s">
-        <v>588</v>
-      </c>
-      <c r="U2" s="50" t="s">
-        <v>625</v>
-      </c>
-      <c r="V2" s="50" t="s">
-        <v>589</v>
-      </c>
-      <c r="W2" s="50" t="s">
-        <v>626</v>
-      </c>
-      <c r="X2" s="50" t="s">
-        <v>590</v>
-      </c>
-      <c r="Y2" s="50" t="s">
-        <v>627</v>
-      </c>
-      <c r="Z2" s="50" t="s">
-        <v>591</v>
-      </c>
-      <c r="AA2" s="50" t="s">
-        <v>628</v>
       </c>
       <c r="AB2" s="50"/>
       <c r="AC2" s="50"/>
@@ -6652,189 +6621,189 @@
         <v>DCH</v>
       </c>
       <c r="D3" s="51" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="E3" s="51" t="s">
         <v>24</v>
       </c>
       <c r="F3" s="51" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="G3" s="51" t="s">
+        <v>622</v>
+      </c>
+      <c r="H3" s="51" t="s">
+        <v>623</v>
+      </c>
+      <c r="I3" s="51" t="s">
+        <v>624</v>
+      </c>
+      <c r="J3" s="51" t="s">
+        <v>585</v>
+      </c>
+      <c r="K3" s="51" t="s">
+        <v>625</v>
+      </c>
+      <c r="L3" s="51" t="s">
+        <v>586</v>
+      </c>
+      <c r="M3" s="51" t="s">
+        <v>626</v>
+      </c>
+      <c r="N3" s="51" t="s">
+        <v>587</v>
+      </c>
+      <c r="O3" s="51" t="s">
+        <v>627</v>
+      </c>
+      <c r="P3" s="51" t="s">
+        <v>588</v>
+      </c>
+      <c r="Q3" s="51" t="s">
+        <v>628</v>
+      </c>
+      <c r="R3" s="51" t="s">
+        <v>589</v>
+      </c>
+      <c r="S3" s="51" t="s">
         <v>629</v>
       </c>
-      <c r="H3" s="51" t="s">
+      <c r="T3" s="51" t="s">
+        <v>590</v>
+      </c>
+      <c r="U3" s="51" t="s">
         <v>630</v>
       </c>
-      <c r="I3" s="51" t="s">
+      <c r="V3" s="51" t="s">
+        <v>591</v>
+      </c>
+      <c r="W3" s="51" t="s">
         <v>631</v>
       </c>
-      <c r="J3" s="51" t="s">
+      <c r="X3" s="51" t="s">
         <v>592</v>
       </c>
-      <c r="K3" s="51" t="s">
+      <c r="Y3" s="51" t="s">
         <v>632</v>
       </c>
-      <c r="L3" s="51" t="s">
+      <c r="Z3" s="51" t="s">
         <v>593</v>
       </c>
-      <c r="M3" s="51" t="s">
+      <c r="AA3" s="51" t="s">
         <v>633</v>
       </c>
-      <c r="N3" s="51" t="s">
+      <c r="AB3" s="51" t="s">
         <v>594</v>
       </c>
-      <c r="O3" s="51" t="s">
+      <c r="AC3" s="51" t="s">
         <v>634</v>
       </c>
-      <c r="P3" s="51" t="s">
+      <c r="AD3" s="51" t="s">
         <v>595</v>
       </c>
-      <c r="Q3" s="51" t="s">
+      <c r="AE3" s="51" t="s">
         <v>635</v>
       </c>
-      <c r="R3" s="51" t="s">
+      <c r="AF3" s="51" t="s">
         <v>596</v>
       </c>
-      <c r="S3" s="51" t="s">
+      <c r="AG3" s="51" t="s">
         <v>636</v>
       </c>
-      <c r="T3" s="51" t="s">
+      <c r="AH3" s="51" t="s">
         <v>597</v>
       </c>
-      <c r="U3" s="51" t="s">
+      <c r="AI3" s="51" t="s">
         <v>637</v>
       </c>
-      <c r="V3" s="51" t="s">
+      <c r="AJ3" s="51" t="s">
         <v>598</v>
       </c>
-      <c r="W3" s="51" t="s">
+      <c r="AK3" s="51" t="s">
         <v>638</v>
       </c>
-      <c r="X3" s="51" t="s">
+      <c r="AL3" s="51" t="s">
         <v>599</v>
       </c>
-      <c r="Y3" s="51" t="s">
+      <c r="AM3" s="51" t="s">
         <v>639</v>
       </c>
-      <c r="Z3" s="51" t="s">
+      <c r="AN3" s="51" t="s">
         <v>600</v>
       </c>
-      <c r="AA3" s="51" t="s">
+      <c r="AO3" s="51" t="s">
         <v>640</v>
       </c>
-      <c r="AB3" s="51" t="s">
+      <c r="AP3" s="51" t="s">
         <v>601</v>
       </c>
-      <c r="AC3" s="51" t="s">
+      <c r="AQ3" s="51" t="s">
         <v>641</v>
       </c>
-      <c r="AD3" s="51" t="s">
+      <c r="AR3" s="51" t="s">
         <v>602</v>
       </c>
-      <c r="AE3" s="51" t="s">
+      <c r="AS3" s="51" t="s">
         <v>642</v>
       </c>
-      <c r="AF3" s="51" t="s">
+      <c r="AT3" s="51" t="s">
         <v>603</v>
       </c>
-      <c r="AG3" s="51" t="s">
+      <c r="AU3" s="51" t="s">
         <v>643</v>
       </c>
-      <c r="AH3" s="51" t="s">
+      <c r="AV3" s="51" t="s">
         <v>604</v>
       </c>
-      <c r="AI3" s="51" t="s">
+      <c r="AW3" s="51" t="s">
         <v>644</v>
       </c>
-      <c r="AJ3" s="51" t="s">
+      <c r="AX3" s="51" t="s">
         <v>605</v>
       </c>
-      <c r="AK3" s="51" t="s">
+      <c r="AY3" s="51" t="s">
         <v>645</v>
       </c>
-      <c r="AL3" s="51" t="s">
+      <c r="AZ3" s="51" t="s">
         <v>606</v>
       </c>
-      <c r="AM3" s="51" t="s">
+      <c r="BA3" s="51" t="s">
         <v>646</v>
       </c>
-      <c r="AN3" s="51" t="s">
+      <c r="BB3" s="51" t="s">
         <v>607</v>
       </c>
-      <c r="AO3" s="51" t="s">
+      <c r="BC3" s="51" t="s">
         <v>647</v>
       </c>
-      <c r="AP3" s="51" t="s">
+      <c r="BD3" s="51" t="s">
         <v>608</v>
       </c>
-      <c r="AQ3" s="51" t="s">
+      <c r="BE3" s="51" t="s">
         <v>648</v>
       </c>
-      <c r="AR3" s="51" t="s">
+      <c r="BF3" s="51" t="s">
         <v>609</v>
       </c>
-      <c r="AS3" s="51" t="s">
+      <c r="BG3" s="51" t="s">
         <v>649</v>
       </c>
-      <c r="AT3" s="51" t="s">
+      <c r="BH3" s="51" t="s">
         <v>610</v>
       </c>
-      <c r="AU3" s="51" t="s">
+      <c r="BI3" s="51" t="s">
         <v>650</v>
       </c>
-      <c r="AV3" s="51" t="s">
+      <c r="BJ3" s="51" t="s">
         <v>611</v>
       </c>
-      <c r="AW3" s="51" t="s">
+      <c r="BK3" s="51" t="s">
         <v>651</v>
-      </c>
-      <c r="AX3" s="51" t="s">
-        <v>612</v>
-      </c>
-      <c r="AY3" s="51" t="s">
-        <v>652</v>
-      </c>
-      <c r="AZ3" s="51" t="s">
-        <v>613</v>
-      </c>
-      <c r="BA3" s="51" t="s">
-        <v>653</v>
-      </c>
-      <c r="BB3" s="51" t="s">
-        <v>614</v>
-      </c>
-      <c r="BC3" s="51" t="s">
-        <v>654</v>
-      </c>
-      <c r="BD3" s="51" t="s">
-        <v>615</v>
-      </c>
-      <c r="BE3" s="51" t="s">
-        <v>655</v>
-      </c>
-      <c r="BF3" s="51" t="s">
-        <v>616</v>
-      </c>
-      <c r="BG3" s="51" t="s">
-        <v>656</v>
-      </c>
-      <c r="BH3" s="51" t="s">
-        <v>617</v>
-      </c>
-      <c r="BI3" s="51" t="s">
-        <v>657</v>
-      </c>
-      <c r="BJ3" s="51" t="s">
-        <v>618</v>
-      </c>
-      <c r="BK3" s="51" t="s">
-        <v>658</v>
       </c>
     </row>
     <row r="4" spans="1:63" x14ac:dyDescent="0.3">
       <c r="J4" s="1"/>
-      <c r="AA4" s="111"/>
+      <c r="AA4" s="108"/>
     </row>
     <row r="10" spans="1:63" x14ac:dyDescent="0.3">
       <c r="J10" s="1"/>
@@ -6967,10 +6936,10 @@
         <v>112</v>
       </c>
       <c r="M1" s="79" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="N1" s="72" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
       <c r="O1" s="101" t="s">
         <v>122</v>
@@ -12188,7 +12157,7 @@
         <v>DCH</v>
       </c>
       <c r="D2" s="50" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="E2" s="50" t="s">
         <v>24</v>
@@ -12205,7 +12174,7 @@
         <v>COM</v>
       </c>
       <c r="D3" s="51" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="E3" s="51" t="s">
         <v>24</v>
@@ -12222,7 +12191,7 @@
         <v>CS</v>
       </c>
       <c r="D4" s="50" t="s">
-        <v>660</v>
+        <v>653</v>
       </c>
       <c r="E4" s="50" t="s">
         <v>24</v>
@@ -12239,7 +12208,7 @@
         <v>DIS</v>
       </c>
       <c r="D5" s="51" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="E5" s="51" t="s">
         <v>24</v>
@@ -12256,7 +12225,7 @@
         <v>DOIP</v>
       </c>
       <c r="D6" s="50" t="s">
-        <v>662</v>
+        <v>655</v>
       </c>
       <c r="E6" s="50" t="s">
         <v>24</v>
@@ -12273,7 +12242,7 @@
         <v>DTG</v>
       </c>
       <c r="D7" s="51" t="s">
-        <v>663</v>
+        <v>656</v>
       </c>
       <c r="E7" s="51" t="s">
         <v>24</v>
@@ -12290,7 +12259,7 @@
         <v>IF</v>
       </c>
       <c r="D8" s="50" t="s">
-        <v>664</v>
+        <v>657</v>
       </c>
       <c r="E8" s="50" t="s">
         <v>24</v>
@@ -12307,7 +12276,7 @@
         <v>BDP</v>
       </c>
       <c r="D9" s="51" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="E9" s="51" t="s">
         <v>24</v>
@@ -12324,7 +12293,7 @@
         <v>PULS</v>
       </c>
       <c r="D10" s="50" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="E10" s="50" t="s">
         <v>24</v>
@@ -12342,7 +12311,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AF73"/>
+  <dimension ref="A1:AF70"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.25" customWidth="1"/>
@@ -12371,8 +12340,8 @@
     <col min="26" max="26" width="18.75" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="27.75" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="21.125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="10.125" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="15" customWidth="1"/>
     <col min="32" max="32" width="17" customWidth="1"/>
   </cols>
@@ -12476,19 +12445,17 @@
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" s="102"/>
       <c r="B2" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C2" s="74" t="e" cm="1">
         <f t="array" ref="C2">UPPER(INDEX(_xlfn.TEXTSPLIT($D2, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D2" s="74"/>
+      <c r="D2" s="73"/>
       <c r="E2" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="74" t="s">
-        <v>204</v>
-      </c>
+      <c r="F2" s="74"/>
       <c r="G2" s="74" t="s">
         <v>209</v>
       </c>
@@ -12515,7 +12482,7 @@
       </c>
       <c r="O2" s="74" t="str">
         <f t="shared" ref="O2:O6" si="0">SUBSTITUTE(F2,"hazr-","")&amp;"-osdisk"</f>
-        <v>t-cs-chtweb01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P2" s="74">
         <v>64</v>
@@ -12528,7 +12495,7 @@
       <c r="T2" s="74"/>
       <c r="U2" s="74" t="str">
         <f>SUBSTITUTE(F2,"hazr-","")&amp;"-nic"</f>
-        <v>t-cs-chtweb01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V2" s="74" t="b">
         <v>1</v>
@@ -12537,33 +12504,27 @@
         <v>1</v>
       </c>
       <c r="X2" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y2" s="74" t="s">
-        <v>201</v>
-      </c>
-      <c r="Z2" s="74" t="s">
-        <v>207</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y2" s="74"/>
+      <c r="Z2" s="74"/>
       <c r="AA2" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB2" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC2" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD2" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD2" s="74"/>
       <c r="AE2" s="74"/>
       <c r="AF2" s="74"/>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A3" s="102"/>
       <c r="B3" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C3" s="74" t="e" cm="1">
         <f t="array" ref="C3">UPPER(INDEX(_xlfn.TEXTSPLIT($D3, "-"), 3))</f>
@@ -12573,9 +12534,7 @@
       <c r="E3" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="74" t="s">
-        <v>205</v>
-      </c>
+      <c r="F3" s="74"/>
       <c r="G3" s="74" t="s">
         <v>262</v>
       </c>
@@ -12602,7 +12561,7 @@
       </c>
       <c r="O3" s="74" t="str">
         <f t="shared" si="0"/>
-        <v>t-cs-chtintweb01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P3" s="74">
         <v>64</v>
@@ -12615,7 +12574,7 @@
       <c r="T3" s="74"/>
       <c r="U3" s="74" t="str">
         <f t="shared" ref="U3:U66" si="1">SUBSTITUTE(F3,"hazr-","")&amp;"-nic"</f>
-        <v>t-cs-chtintweb01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V3" s="74" t="b">
         <v>1</v>
@@ -12624,45 +12583,37 @@
         <v>1</v>
       </c>
       <c r="X3" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y3" s="74" t="s">
-        <v>202</v>
-      </c>
-      <c r="Z3" s="74" t="s">
-        <v>206</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y3" s="74"/>
+      <c r="Z3" s="74"/>
       <c r="AA3" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB3" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC3" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD3" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD3" s="74"/>
       <c r="AE3" s="74"/>
       <c r="AF3" s="74"/>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A4" s="97"/>
       <c r="B4" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C4" s="74" t="e" cm="1">
         <f t="array" ref="C4">UPPER(INDEX(_xlfn.TEXTSPLIT($D4, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D4" s="74"/>
+      <c r="D4" s="73"/>
       <c r="E4" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="74" t="s">
-        <v>261</v>
-      </c>
+      <c r="F4" s="74"/>
       <c r="G4" s="74" t="s">
         <v>210</v>
       </c>
@@ -12689,7 +12640,7 @@
       </c>
       <c r="O4" s="74" t="str">
         <f t="shared" si="0"/>
-        <v>t-cs-chtap01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P4" s="74">
         <v>64</v>
@@ -12702,7 +12653,7 @@
       <c r="T4" s="74"/>
       <c r="U4" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-cs-chtap01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V4" s="74" t="b">
         <v>1</v>
@@ -12711,45 +12662,37 @@
         <v>1</v>
       </c>
       <c r="X4" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y4" s="74" t="s">
-        <v>202</v>
-      </c>
-      <c r="Z4" s="74" t="s">
-        <v>206</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y4" s="74"/>
+      <c r="Z4" s="74"/>
       <c r="AA4" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB4" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC4" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD4" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD4" s="74"/>
       <c r="AE4" s="74"/>
       <c r="AF4" s="74"/>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A5" s="97"/>
       <c r="B5" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C5" s="74" t="e" cm="1">
         <f t="array" ref="C5">UPPER(INDEX(_xlfn.TEXTSPLIT($D5, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D5" s="74"/>
+      <c r="D5" s="78"/>
       <c r="E5" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="74" t="s">
-        <v>474</v>
-      </c>
+      <c r="F5" s="74"/>
       <c r="G5" s="74" t="s">
         <v>348</v>
       </c>
@@ -12776,7 +12719,7 @@
       </c>
       <c r="O5" s="74" t="str">
         <f t="shared" si="0"/>
-        <v>t-dis-ap01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P5" s="74">
         <v>64</v>
@@ -12789,7 +12732,7 @@
       <c r="T5" s="74"/>
       <c r="U5" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dis-ap01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V5" s="74" t="b">
         <v>1</v>
@@ -12798,45 +12741,37 @@
         <v>1</v>
       </c>
       <c r="X5" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y5" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z5" s="74" t="s">
-        <v>347</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y5" s="74"/>
+      <c r="Z5" s="74"/>
       <c r="AA5" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB5" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC5" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD5" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD5" s="74"/>
       <c r="AE5" s="74"/>
       <c r="AF5" s="74"/>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A6" s="97"/>
       <c r="B6" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C6" s="74" t="e" cm="1">
         <f t="array" ref="C6">UPPER(INDEX(_xlfn.TEXTSPLIT($D6, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D6" s="74"/>
+      <c r="D6" s="88"/>
       <c r="E6" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="74" t="s">
-        <v>475</v>
-      </c>
+      <c r="F6" s="74"/>
       <c r="G6" s="74" t="s">
         <v>349</v>
       </c>
@@ -12863,7 +12798,7 @@
       </c>
       <c r="O6" s="74" t="str">
         <f t="shared" si="0"/>
-        <v>t-dis-adm01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P6" s="74">
         <v>64</v>
@@ -12876,7 +12811,7 @@
       <c r="T6" s="74"/>
       <c r="U6" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dis-adm01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V6" s="74" t="b">
         <v>1</v>
@@ -12885,45 +12820,37 @@
         <v>1</v>
       </c>
       <c r="X6" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y6" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z6" s="74" t="s">
-        <v>347</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y6" s="74"/>
+      <c r="Z6" s="74"/>
       <c r="AA6" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB6" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC6" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD6" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD6" s="74"/>
       <c r="AE6" s="74"/>
       <c r="AF6" s="74"/>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A7" s="97"/>
       <c r="B7" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C7" s="74" t="e" cm="1">
         <f t="array" ref="C7">UPPER(INDEX(_xlfn.TEXTSPLIT($D7, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D7" s="74"/>
+      <c r="D7" s="78"/>
       <c r="E7" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="74" t="s">
-        <v>476</v>
-      </c>
+      <c r="F7" s="74"/>
       <c r="G7" s="74" t="s">
         <v>351</v>
       </c>
@@ -12950,7 +12877,7 @@
       </c>
       <c r="O7" s="74" t="str">
         <f>SUBSTITUTE(F7,"hazr-","")&amp;"-osdisk"</f>
-        <v>t-dis-bbiweb01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P7" s="74">
         <v>64</v>
@@ -12963,7 +12890,7 @@
       <c r="T7" s="74"/>
       <c r="U7" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dis-bbiweb01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V7" s="74" t="b">
         <v>1</v>
@@ -12972,45 +12899,37 @@
         <v>1</v>
       </c>
       <c r="X7" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y7" s="74" t="s">
-        <v>452</v>
-      </c>
-      <c r="Z7" s="74" t="s">
-        <v>350</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y7" s="74"/>
+      <c r="Z7" s="74"/>
       <c r="AA7" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB7" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC7" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD7" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD7" s="74"/>
       <c r="AE7" s="74"/>
       <c r="AF7" s="74"/>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A8" s="97"/>
       <c r="B8" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C8" s="74" t="e" cm="1">
         <f t="array" ref="C8">UPPER(INDEX(_xlfn.TEXTSPLIT($D8, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D8" s="74"/>
+      <c r="D8" s="88"/>
       <c r="E8" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="74" t="s">
-        <v>477</v>
-      </c>
+      <c r="F8" s="74"/>
       <c r="G8" s="74" t="s">
         <v>548</v>
       </c>
@@ -13037,7 +12956,7 @@
       </c>
       <c r="O8" s="74" t="str">
         <f t="shared" ref="O8:O39" si="2">SUBSTITUTE(F8,"hazr-","")&amp;"-osdisk"</f>
-        <v>t-dis-bbicltap01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P8" s="74">
         <v>64</v>
@@ -13050,7 +12969,7 @@
       <c r="T8" s="74"/>
       <c r="U8" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dis-bbicltap01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V8" s="74" t="b">
         <v>1</v>
@@ -13059,45 +12978,37 @@
         <v>1</v>
       </c>
       <c r="X8" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y8" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z8" s="74" t="s">
-        <v>347</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y8" s="74"/>
+      <c r="Z8" s="74"/>
       <c r="AA8" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB8" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC8" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD8" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD8" s="74"/>
       <c r="AE8" s="74"/>
       <c r="AF8" s="74"/>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A9" s="97"/>
       <c r="B9" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C9" s="74" t="e" cm="1">
         <f t="array" ref="C9">UPPER(INDEX(_xlfn.TEXTSPLIT($D9, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D9" s="74"/>
+      <c r="D9" s="78"/>
       <c r="E9" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F9" s="74" t="s">
-        <v>478</v>
-      </c>
+      <c r="F9" s="74"/>
       <c r="G9" s="74" t="s">
         <v>352</v>
       </c>
@@ -13124,7 +13035,7 @@
       </c>
       <c r="O9" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dis-bbimsgap01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P9" s="74">
         <v>64</v>
@@ -13137,7 +13048,7 @@
       <c r="T9" s="74"/>
       <c r="U9" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dis-bbimsgap01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V9" s="74" t="b">
         <v>1</v>
@@ -13146,45 +13057,37 @@
         <v>1</v>
       </c>
       <c r="X9" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y9" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z9" s="74" t="s">
-        <v>347</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y9" s="74"/>
+      <c r="Z9" s="74"/>
       <c r="AA9" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB9" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC9" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD9" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD9" s="74"/>
       <c r="AE9" s="74"/>
       <c r="AF9" s="74"/>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A10" s="97"/>
       <c r="B10" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C10" s="74" t="e" cm="1">
         <f t="array" ref="C10">UPPER(INDEX(_xlfn.TEXTSPLIT($D10, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D10" s="74"/>
+      <c r="D10" s="88"/>
       <c r="E10" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F10" s="74" t="s">
-        <v>479</v>
-      </c>
+      <c r="F10" s="74"/>
       <c r="G10" s="74" t="s">
         <v>353</v>
       </c>
@@ -13211,7 +13114,7 @@
       </c>
       <c r="O10" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dis-walkap01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P10" s="74">
         <v>64</v>
@@ -13224,7 +13127,7 @@
       <c r="T10" s="74"/>
       <c r="U10" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dis-walkap01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V10" s="74" t="b">
         <v>1</v>
@@ -13233,45 +13136,37 @@
         <v>1</v>
       </c>
       <c r="X10" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y10" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z10" s="74" t="s">
-        <v>347</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y10" s="74"/>
+      <c r="Z10" s="74"/>
       <c r="AA10" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB10" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC10" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD10" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD10" s="74"/>
       <c r="AE10" s="74"/>
       <c r="AF10" s="74"/>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A11" s="97"/>
       <c r="B11" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C11" s="74" t="e" cm="1">
         <f t="array" ref="C11">UPPER(INDEX(_xlfn.TEXTSPLIT($D11, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D11" s="74"/>
+      <c r="D11" s="78"/>
       <c r="E11" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="74" t="s">
-        <v>480</v>
-      </c>
+      <c r="F11" s="74"/>
       <c r="G11" s="74" t="s">
         <v>453</v>
       </c>
@@ -13298,7 +13193,7 @@
       </c>
       <c r="O11" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dis-bat01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P11" s="74">
         <v>64</v>
@@ -13311,7 +13206,7 @@
       <c r="T11" s="74"/>
       <c r="U11" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dis-bat01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V11" s="74" t="b">
         <v>1</v>
@@ -13320,45 +13215,37 @@
         <v>1</v>
       </c>
       <c r="X11" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y11" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z11" s="74" t="s">
-        <v>347</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y11" s="74"/>
+      <c r="Z11" s="74"/>
       <c r="AA11" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB11" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC11" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD11" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD11" s="74"/>
       <c r="AE11" s="74"/>
       <c r="AF11" s="74"/>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A12" s="97"/>
       <c r="B12" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C12" s="74" t="e" cm="1">
         <f t="array" ref="C12">UPPER(INDEX(_xlfn.TEXTSPLIT($D12, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D12" s="74"/>
+      <c r="D12" s="88"/>
       <c r="E12" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F12" s="74" t="s">
-        <v>481</v>
-      </c>
+      <c r="F12" s="74"/>
       <c r="G12" s="74" t="s">
         <v>354</v>
       </c>
@@ -13385,7 +13272,7 @@
       </c>
       <c r="O12" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dis-drvcltap01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P12" s="74">
         <v>64</v>
@@ -13398,7 +13285,7 @@
       <c r="T12" s="74"/>
       <c r="U12" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dis-drvcltap01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V12" s="74" t="b">
         <v>1</v>
@@ -13407,45 +13294,37 @@
         <v>1</v>
       </c>
       <c r="X12" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y12" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z12" s="74" t="s">
-        <v>347</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y12" s="74"/>
+      <c r="Z12" s="74"/>
       <c r="AA12" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB12" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC12" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD12" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD12" s="74"/>
       <c r="AE12" s="74"/>
       <c r="AF12" s="74"/>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A13" s="97"/>
       <c r="B13" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C13" s="74" t="e" cm="1">
         <f t="array" ref="C13">UPPER(INDEX(_xlfn.TEXTSPLIT($D13, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D13" s="74"/>
+      <c r="D13" s="78"/>
       <c r="E13" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F13" s="74" t="s">
-        <v>482</v>
-      </c>
+      <c r="F13" s="74"/>
       <c r="G13" s="74" t="s">
         <v>355</v>
       </c>
@@ -13472,7 +13351,7 @@
       </c>
       <c r="O13" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dis-walkweb01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P13" s="74">
         <v>64</v>
@@ -13485,7 +13364,7 @@
       <c r="T13" s="74"/>
       <c r="U13" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dis-walkweb01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V13" s="74" t="b">
         <v>1</v>
@@ -13494,45 +13373,37 @@
         <v>1</v>
       </c>
       <c r="X13" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y13" s="74" t="s">
-        <v>452</v>
-      </c>
-      <c r="Z13" s="74" t="s">
-        <v>350</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y13" s="74"/>
+      <c r="Z13" s="74"/>
       <c r="AA13" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB13" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC13" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD13" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD13" s="74"/>
       <c r="AE13" s="74"/>
       <c r="AF13" s="74"/>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A14" s="97"/>
       <c r="B14" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C14" s="74" t="e" cm="1">
         <f t="array" ref="C14">UPPER(INDEX(_xlfn.TEXTSPLIT($D14, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D14" s="74"/>
+      <c r="D14" s="88"/>
       <c r="E14" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="74" t="s">
-        <v>483</v>
-      </c>
+      <c r="F14" s="74"/>
       <c r="G14" s="74" t="s">
         <v>454</v>
       </c>
@@ -13559,7 +13430,7 @@
       </c>
       <c r="O14" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dis-drvmsgap01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P14" s="74">
         <v>64</v>
@@ -13572,7 +13443,7 @@
       <c r="T14" s="74"/>
       <c r="U14" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dis-drvmsgap01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V14" s="74" t="b">
         <v>1</v>
@@ -13581,45 +13452,37 @@
         <v>1</v>
       </c>
       <c r="X14" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y14" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z14" s="74" t="s">
-        <v>347</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y14" s="74"/>
+      <c r="Z14" s="74"/>
       <c r="AA14" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB14" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC14" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD14" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD14" s="74"/>
       <c r="AE14" s="74"/>
       <c r="AF14" s="74"/>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A15" s="97"/>
       <c r="B15" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C15" s="74" t="e" cm="1">
         <f t="array" ref="C15">UPPER(INDEX(_xlfn.TEXTSPLIT($D15, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D15" s="74"/>
+      <c r="D15" s="78"/>
       <c r="E15" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F15" s="74" t="s">
-        <v>484</v>
-      </c>
+      <c r="F15" s="74"/>
       <c r="G15" s="74" t="s">
         <v>455</v>
       </c>
@@ -13646,7 +13509,7 @@
       </c>
       <c r="O15" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dis-web01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P15" s="74">
         <v>64</v>
@@ -13659,7 +13522,7 @@
       <c r="T15" s="74"/>
       <c r="U15" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dis-web01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V15" s="74" t="b">
         <v>1</v>
@@ -13668,45 +13531,37 @@
         <v>1</v>
       </c>
       <c r="X15" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y15" s="74" t="s">
-        <v>452</v>
-      </c>
-      <c r="Z15" s="74" t="s">
-        <v>350</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y15" s="74"/>
+      <c r="Z15" s="74"/>
       <c r="AA15" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB15" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC15" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD15" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD15" s="74"/>
       <c r="AE15" s="74"/>
       <c r="AF15" s="74"/>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A16" s="97"/>
       <c r="B16" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C16" s="74" t="e" cm="1">
         <f t="array" ref="C16">UPPER(INDEX(_xlfn.TEXTSPLIT($D16, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D16" s="74"/>
+      <c r="D16" s="88"/>
       <c r="E16" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F16" s="74" t="s">
-        <v>485</v>
-      </c>
+      <c r="F16" s="74"/>
       <c r="G16" s="74" t="s">
         <v>356</v>
       </c>
@@ -13733,7 +13588,7 @@
       </c>
       <c r="O16" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dis-cmsadm01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P16" s="74">
         <v>64</v>
@@ -13746,7 +13601,7 @@
       <c r="T16" s="74"/>
       <c r="U16" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dis-cmsadm01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V16" s="74" t="b">
         <v>1</v>
@@ -13755,45 +13610,37 @@
         <v>1</v>
       </c>
       <c r="X16" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y16" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z16" s="74" t="s">
-        <v>347</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y16" s="74"/>
+      <c r="Z16" s="74"/>
       <c r="AA16" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB16" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC16" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD16" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD16" s="74"/>
       <c r="AE16" s="74"/>
       <c r="AF16" s="74"/>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A17" s="97"/>
       <c r="B17" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C17" s="74" t="e" cm="1">
         <f t="array" ref="C17">UPPER(INDEX(_xlfn.TEXTSPLIT($D17, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D17" s="74"/>
+      <c r="D17" s="78"/>
       <c r="E17" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F17" s="74" t="s">
-        <v>486</v>
-      </c>
+      <c r="F17" s="74"/>
       <c r="G17" s="74" t="s">
         <v>357</v>
       </c>
@@ -13820,7 +13667,7 @@
       </c>
       <c r="O17" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dis-cmsap01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P17" s="74">
         <v>64</v>
@@ -13833,7 +13680,7 @@
       <c r="T17" s="74"/>
       <c r="U17" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dis-cmsap01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V17" s="74" t="b">
         <v>1</v>
@@ -13842,45 +13689,37 @@
         <v>1</v>
       </c>
       <c r="X17" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y17" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z17" s="74" t="s">
-        <v>347</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y17" s="74"/>
+      <c r="Z17" s="74"/>
       <c r="AA17" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB17" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC17" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD17" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD17" s="74"/>
       <c r="AE17" s="74"/>
       <c r="AF17" s="74"/>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A18" s="97"/>
       <c r="B18" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C18" s="74" t="e" cm="1">
         <f t="array" ref="C18">UPPER(INDEX(_xlfn.TEXTSPLIT($D18, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D18" s="74"/>
+      <c r="D18" s="88"/>
       <c r="E18" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F18" s="74" t="s">
-        <v>487</v>
-      </c>
+      <c r="F18" s="74"/>
       <c r="G18" s="74" t="s">
         <v>358</v>
       </c>
@@ -13907,7 +13746,7 @@
       </c>
       <c r="O18" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dis-cmsweb01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P18" s="74">
         <v>64</v>
@@ -13920,7 +13759,7 @@
       <c r="T18" s="74"/>
       <c r="U18" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dis-cmsweb01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V18" s="74" t="b">
         <v>1</v>
@@ -13929,45 +13768,37 @@
         <v>1</v>
       </c>
       <c r="X18" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y18" s="74" t="s">
-        <v>452</v>
-      </c>
-      <c r="Z18" s="74" t="s">
-        <v>350</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y18" s="74"/>
+      <c r="Z18" s="74"/>
       <c r="AA18" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB18" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC18" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD18" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD18" s="74"/>
       <c r="AE18" s="74"/>
       <c r="AF18" s="74"/>
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A19" s="97"/>
       <c r="B19" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C19" s="74" t="e" cm="1">
         <f t="array" ref="C19">UPPER(INDEX(_xlfn.TEXTSPLIT($D19, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D19" s="74"/>
+      <c r="D19" s="78"/>
       <c r="E19" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F19" s="74" t="s">
-        <v>488</v>
-      </c>
+      <c r="F19" s="74"/>
       <c r="G19" s="74" t="s">
         <v>359</v>
       </c>
@@ -13994,7 +13825,7 @@
       </c>
       <c r="O19" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dis-cmbsap01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P19" s="74">
         <v>64</v>
@@ -14007,7 +13838,7 @@
       <c r="T19" s="74"/>
       <c r="U19" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dis-cmbsap01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V19" s="74" t="b">
         <v>1</v>
@@ -14016,45 +13847,37 @@
         <v>1</v>
       </c>
       <c r="X19" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y19" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z19" s="74" t="s">
-        <v>347</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y19" s="74"/>
+      <c r="Z19" s="74"/>
       <c r="AA19" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB19" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC19" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD19" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD19" s="74"/>
       <c r="AE19" s="74"/>
       <c r="AF19" s="74"/>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A20" s="97"/>
       <c r="B20" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C20" s="74" t="e" cm="1">
         <f t="array" ref="C20">UPPER(INDEX(_xlfn.TEXTSPLIT($D20, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D20" s="74"/>
+      <c r="D20" s="88"/>
       <c r="E20" s="74" t="s">
-        <v>568</v>
-      </c>
-      <c r="F20" s="74" t="s">
-        <v>489</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="F20" s="74"/>
       <c r="G20" s="74" t="s">
         <v>456</v>
       </c>
@@ -14081,7 +13904,7 @@
       </c>
       <c r="O20" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dis-dfir01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P20" s="74">
         <v>128</v>
@@ -14094,7 +13917,7 @@
       <c r="T20" s="74"/>
       <c r="U20" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dis-dfir01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V20" s="74" t="b">
         <v>1</v>
@@ -14103,45 +13926,37 @@
         <v>1</v>
       </c>
       <c r="X20" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y20" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z20" s="74" t="s">
-        <v>347</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y20" s="74"/>
+      <c r="Z20" s="74"/>
       <c r="AA20" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB20" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC20" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD20" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD20" s="74"/>
       <c r="AE20" s="74"/>
       <c r="AF20" s="74"/>
     </row>
     <row r="21" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A21" s="97"/>
       <c r="B21" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C21" s="74" t="e" cm="1">
         <f t="array" ref="C21">UPPER(INDEX(_xlfn.TEXTSPLIT($D21, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D21" s="74"/>
+      <c r="D21" s="78"/>
       <c r="E21" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F21" s="74" t="s">
-        <v>490</v>
-      </c>
+      <c r="F21" s="74"/>
       <c r="G21" s="74" t="s">
         <v>361</v>
       </c>
@@ -14168,7 +13983,7 @@
       </c>
       <c r="O21" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dtg-ingap01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P21" s="74">
         <v>64</v>
@@ -14181,7 +13996,7 @@
       <c r="T21" s="74"/>
       <c r="U21" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dtg-ingap01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V21" s="74" t="b">
         <v>1</v>
@@ -14190,45 +14005,37 @@
         <v>1</v>
       </c>
       <c r="X21" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y21" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z21" s="74" t="s">
-        <v>360</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y21" s="74"/>
+      <c r="Z21" s="74"/>
       <c r="AA21" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB21" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC21" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD21" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD21" s="74"/>
       <c r="AE21" s="74"/>
       <c r="AF21" s="74"/>
     </row>
     <row r="22" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A22" s="97"/>
       <c r="B22" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C22" s="74" t="e" cm="1">
         <f t="array" ref="C22">UPPER(INDEX(_xlfn.TEXTSPLIT($D22, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D22" s="74"/>
+      <c r="D22" s="88"/>
       <c r="E22" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F22" s="74" t="s">
-        <v>491</v>
-      </c>
+      <c r="F22" s="74"/>
       <c r="G22" s="74" t="s">
         <v>362</v>
       </c>
@@ -14255,7 +14062,7 @@
       </c>
       <c r="O22" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dtg-ap01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P22" s="74">
         <v>64</v>
@@ -14268,7 +14075,7 @@
       <c r="T22" s="74"/>
       <c r="U22" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dtg-ap01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V22" s="74" t="b">
         <v>1</v>
@@ -14277,45 +14084,37 @@
         <v>1</v>
       </c>
       <c r="X22" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y22" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z22" s="74" t="s">
-        <v>360</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y22" s="74"/>
+      <c r="Z22" s="74"/>
       <c r="AA22" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB22" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC22" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD22" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD22" s="74"/>
       <c r="AE22" s="74"/>
       <c r="AF22" s="74"/>
     </row>
     <row r="23" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A23" s="97"/>
       <c r="B23" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C23" s="74" t="e" cm="1">
         <f t="array" ref="C23">UPPER(INDEX(_xlfn.TEXTSPLIT($D23, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D23" s="74"/>
+      <c r="D23" s="78"/>
       <c r="E23" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F23" s="74" t="s">
-        <v>492</v>
-      </c>
+      <c r="F23" s="74"/>
       <c r="G23" s="74" t="s">
         <v>363</v>
       </c>
@@ -14342,7 +14141,7 @@
       </c>
       <c r="O23" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dtg-extgeoap01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P23" s="74">
         <v>64</v>
@@ -14355,7 +14154,7 @@
       <c r="T23" s="74"/>
       <c r="U23" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dtg-extgeoap01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V23" s="74" t="b">
         <v>1</v>
@@ -14364,45 +14163,37 @@
         <v>1</v>
       </c>
       <c r="X23" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y23" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z23" s="74" t="s">
-        <v>360</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y23" s="74"/>
+      <c r="Z23" s="74"/>
       <c r="AA23" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB23" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC23" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD23" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD23" s="74"/>
       <c r="AE23" s="74"/>
       <c r="AF23" s="74"/>
     </row>
     <row r="24" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A24" s="97"/>
       <c r="B24" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C24" s="74" t="e" cm="1">
         <f t="array" ref="C24">UPPER(INDEX(_xlfn.TEXTSPLIT($D24, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D24" s="74"/>
+      <c r="D24" s="88"/>
       <c r="E24" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F24" s="74" t="s">
-        <v>493</v>
-      </c>
+      <c r="F24" s="74"/>
       <c r="G24" s="74" t="s">
         <v>364</v>
       </c>
@@ -14429,7 +14220,7 @@
       </c>
       <c r="O24" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dtg-geoap01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P24" s="74">
         <v>64</v>
@@ -14442,7 +14233,7 @@
       <c r="T24" s="74"/>
       <c r="U24" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dtg-geoap01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V24" s="74" t="b">
         <v>1</v>
@@ -14451,45 +14242,37 @@
         <v>1</v>
       </c>
       <c r="X24" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y24" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z24" s="74" t="s">
-        <v>360</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y24" s="74"/>
+      <c r="Z24" s="74"/>
       <c r="AA24" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB24" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC24" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD24" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD24" s="74"/>
       <c r="AE24" s="74"/>
       <c r="AF24" s="74"/>
     </row>
     <row r="25" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A25" s="97"/>
       <c r="B25" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C25" s="74" t="e" cm="1">
         <f t="array" ref="C25">UPPER(INDEX(_xlfn.TEXTSPLIT($D25, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D25" s="74"/>
+      <c r="D25" s="78"/>
       <c r="E25" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F25" s="74" t="s">
-        <v>494</v>
-      </c>
+      <c r="F25" s="74"/>
       <c r="G25" s="74" t="s">
         <v>366</v>
       </c>
@@ -14516,7 +14299,7 @@
       </c>
       <c r="O25" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dtg-mq01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P25" s="74">
         <v>64</v>
@@ -14529,7 +14312,7 @@
       <c r="T25" s="74"/>
       <c r="U25" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dtg-mq01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V25" s="74" t="b">
         <v>1</v>
@@ -14538,45 +14321,37 @@
         <v>1</v>
       </c>
       <c r="X25" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y25" s="74" t="s">
-        <v>452</v>
-      </c>
-      <c r="Z25" s="74" t="s">
-        <v>365</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y25" s="74"/>
+      <c r="Z25" s="74"/>
       <c r="AA25" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB25" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC25" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD25" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD25" s="74"/>
       <c r="AE25" s="74"/>
       <c r="AF25" s="74"/>
     </row>
     <row r="26" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A26" s="97"/>
       <c r="B26" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C26" s="74" t="e" cm="1">
         <f t="array" ref="C26">UPPER(INDEX(_xlfn.TEXTSPLIT($D26, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D26" s="74"/>
+      <c r="D26" s="88"/>
       <c r="E26" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F26" s="74" t="s">
-        <v>495</v>
-      </c>
+      <c r="F26" s="74"/>
       <c r="G26" s="74" t="s">
         <v>367</v>
       </c>
@@ -14603,7 +14378,7 @@
       </c>
       <c r="O26" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dtg-admweb01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P26" s="74">
         <v>64</v>
@@ -14616,7 +14391,7 @@
       <c r="T26" s="74"/>
       <c r="U26" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dtg-admweb01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V26" s="74" t="b">
         <v>1</v>
@@ -14625,45 +14400,37 @@
         <v>1</v>
       </c>
       <c r="X26" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y26" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z26" s="74" t="s">
-        <v>360</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y26" s="74"/>
+      <c r="Z26" s="74"/>
       <c r="AA26" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB26" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC26" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD26" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD26" s="74"/>
       <c r="AE26" s="74"/>
       <c r="AF26" s="74"/>
     </row>
     <row r="27" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A27" s="97"/>
       <c r="B27" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C27" s="74" t="e" cm="1">
         <f t="array" ref="C27">UPPER(INDEX(_xlfn.TEXTSPLIT($D27, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D27" s="74"/>
+      <c r="D27" s="78"/>
       <c r="E27" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F27" s="74" t="s">
-        <v>496</v>
-      </c>
+      <c r="F27" s="74"/>
       <c r="G27" s="74" t="s">
         <v>368</v>
       </c>
@@ -14690,7 +14457,7 @@
       </c>
       <c r="O27" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dtg-admap01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P27" s="74">
         <v>64</v>
@@ -14703,7 +14470,7 @@
       <c r="T27" s="74"/>
       <c r="U27" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dtg-admap01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V27" s="74" t="b">
         <v>1</v>
@@ -14712,45 +14479,37 @@
         <v>1</v>
       </c>
       <c r="X27" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y27" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z27" s="74" t="s">
-        <v>360</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y27" s="74"/>
+      <c r="Z27" s="74"/>
       <c r="AA27" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB27" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC27" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD27" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD27" s="74"/>
       <c r="AE27" s="74"/>
       <c r="AF27" s="74"/>
     </row>
     <row r="28" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A28" s="97"/>
       <c r="B28" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C28" s="74" t="e" cm="1">
         <f t="array" ref="C28">UPPER(INDEX(_xlfn.TEXTSPLIT($D28, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D28" s="74"/>
+      <c r="D28" s="88"/>
       <c r="E28" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F28" s="74" t="s">
-        <v>497</v>
-      </c>
+      <c r="F28" s="74"/>
       <c r="G28" s="74" t="s">
         <v>457</v>
       </c>
@@ -14777,7 +14536,7 @@
       </c>
       <c r="O28" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dtg-dtoms01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P28" s="74">
         <v>64</v>
@@ -14790,7 +14549,7 @@
       <c r="T28" s="74"/>
       <c r="U28" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dtg-dtoms01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V28" s="74" t="b">
         <v>1</v>
@@ -14799,45 +14558,37 @@
         <v>1</v>
       </c>
       <c r="X28" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y28" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z28" s="74" t="s">
-        <v>360</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y28" s="74"/>
+      <c r="Z28" s="74"/>
       <c r="AA28" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB28" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC28" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD28" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD28" s="74"/>
       <c r="AE28" s="74"/>
       <c r="AF28" s="74"/>
     </row>
     <row r="29" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A29" s="97"/>
       <c r="B29" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C29" s="74" t="e" cm="1">
         <f t="array" ref="C29">UPPER(INDEX(_xlfn.TEXTSPLIT($D29, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D29" s="74"/>
+      <c r="D29" s="78"/>
       <c r="E29" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F29" s="74" t="s">
-        <v>498</v>
-      </c>
+      <c r="F29" s="74"/>
       <c r="G29" s="74" t="s">
         <v>459</v>
       </c>
@@ -14864,7 +14615,7 @@
       </c>
       <c r="O29" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dtg-tsdb01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P29" s="74">
         <v>64</v>
@@ -14877,7 +14628,7 @@
       <c r="T29" s="74"/>
       <c r="U29" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dtg-tsdb01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V29" s="74" t="b">
         <v>1</v>
@@ -14886,45 +14637,37 @@
         <v>1</v>
       </c>
       <c r="X29" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y29" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z29" s="74" t="s">
-        <v>458</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y29" s="74"/>
+      <c r="Z29" s="74"/>
       <c r="AA29" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB29" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC29" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD29" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD29" s="74"/>
       <c r="AE29" s="74"/>
       <c r="AF29" s="74"/>
     </row>
     <row r="30" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A30" s="97"/>
       <c r="B30" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C30" s="74" t="e" cm="1">
         <f t="array" ref="C30">UPPER(INDEX(_xlfn.TEXTSPLIT($D30, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D30" s="74"/>
+      <c r="D30" s="88"/>
       <c r="E30" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F30" s="74" t="s">
-        <v>499</v>
-      </c>
+      <c r="F30" s="74"/>
       <c r="G30" s="74" t="s">
         <v>369</v>
       </c>
@@ -14951,7 +14694,7 @@
       </c>
       <c r="O30" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dtg-web01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P30" s="74">
         <v>64</v>
@@ -14964,7 +14707,7 @@
       <c r="T30" s="74"/>
       <c r="U30" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dtg-web01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V30" s="74" t="b">
         <v>1</v>
@@ -14973,45 +14716,37 @@
         <v>1</v>
       </c>
       <c r="X30" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y30" s="74" t="s">
-        <v>452</v>
-      </c>
-      <c r="Z30" s="74" t="s">
-        <v>365</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y30" s="74"/>
+      <c r="Z30" s="74"/>
       <c r="AA30" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB30" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC30" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD30" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD30" s="74"/>
       <c r="AE30" s="74"/>
       <c r="AF30" s="74"/>
     </row>
     <row r="31" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A31" s="97"/>
       <c r="B31" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C31" s="74" t="e" cm="1">
         <f t="array" ref="C31">UPPER(INDEX(_xlfn.TEXTSPLIT($D31, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D31" s="74"/>
+      <c r="D31" s="78"/>
       <c r="E31" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F31" s="74" t="s">
-        <v>500</v>
-      </c>
+      <c r="F31" s="74"/>
       <c r="G31" s="74" t="s">
         <v>460</v>
       </c>
@@ -15038,7 +14773,7 @@
       </c>
       <c r="O31" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dtg-zkp01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P31" s="74">
         <v>64</v>
@@ -15051,7 +14786,7 @@
       <c r="T31" s="74"/>
       <c r="U31" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dtg-zkp01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V31" s="74" t="b">
         <v>1</v>
@@ -15060,45 +14795,37 @@
         <v>1</v>
       </c>
       <c r="X31" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y31" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z31" s="74" t="s">
-        <v>360</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y31" s="74"/>
+      <c r="Z31" s="74"/>
       <c r="AA31" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB31" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC31" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD31" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD31" s="74"/>
       <c r="AE31" s="74"/>
       <c r="AF31" s="74"/>
     </row>
     <row r="32" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A32" s="97"/>
       <c r="B32" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C32" s="74" t="e" cm="1">
         <f t="array" ref="C32">UPPER(INDEX(_xlfn.TEXTSPLIT($D32, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D32" s="74"/>
+      <c r="D32" s="88"/>
       <c r="E32" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F32" s="74" t="s">
-        <v>501</v>
-      </c>
+      <c r="F32" s="74"/>
       <c r="G32" s="74" t="s">
         <v>461</v>
       </c>
@@ -15125,7 +14852,7 @@
       </c>
       <c r="O32" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dtg-zkp02-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P32" s="74">
         <v>64</v>
@@ -15138,7 +14865,7 @@
       <c r="T32" s="74"/>
       <c r="U32" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dtg-zkp02-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V32" s="74" t="b">
         <v>1</v>
@@ -15147,45 +14874,37 @@
         <v>1</v>
       </c>
       <c r="X32" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y32" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z32" s="74" t="s">
-        <v>360</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y32" s="74"/>
+      <c r="Z32" s="74"/>
       <c r="AA32" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB32" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC32" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD32" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD32" s="74"/>
       <c r="AE32" s="74"/>
       <c r="AF32" s="74"/>
     </row>
     <row r="33" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A33" s="97"/>
       <c r="B33" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C33" s="74" t="e" cm="1">
         <f t="array" ref="C33">UPPER(INDEX(_xlfn.TEXTSPLIT($D33, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D33" s="74"/>
+      <c r="D33" s="78"/>
       <c r="E33" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F33" s="74" t="s">
-        <v>502</v>
-      </c>
+      <c r="F33" s="74"/>
       <c r="G33" s="74" t="s">
         <v>462</v>
       </c>
@@ -15212,7 +14931,7 @@
       </c>
       <c r="O33" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dtg-zkp03-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P33" s="74">
         <v>64</v>
@@ -15225,7 +14944,7 @@
       <c r="T33" s="74"/>
       <c r="U33" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dtg-zkp03-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V33" s="74" t="b">
         <v>1</v>
@@ -15234,45 +14953,37 @@
         <v>1</v>
       </c>
       <c r="X33" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y33" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z33" s="74" t="s">
-        <v>360</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y33" s="74"/>
+      <c r="Z33" s="74"/>
       <c r="AA33" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB33" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC33" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD33" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD33" s="74"/>
       <c r="AE33" s="74"/>
       <c r="AF33" s="74"/>
     </row>
     <row r="34" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A34" s="97"/>
       <c r="B34" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C34" s="74" t="e" cm="1">
         <f t="array" ref="C34">UPPER(INDEX(_xlfn.TEXTSPLIT($D34, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D34" s="74"/>
+      <c r="D34" s="88"/>
       <c r="E34" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F34" s="74" t="s">
-        <v>503</v>
-      </c>
+      <c r="F34" s="74"/>
       <c r="G34" s="74" t="s">
         <v>463</v>
       </c>
@@ -15299,7 +15010,7 @@
       </c>
       <c r="O34" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dtg-kfk01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P34" s="74">
         <v>64</v>
@@ -15312,7 +15023,7 @@
       <c r="T34" s="74"/>
       <c r="U34" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dtg-kfk01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V34" s="74" t="b">
         <v>1</v>
@@ -15321,45 +15032,37 @@
         <v>1</v>
       </c>
       <c r="X34" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y34" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z34" s="74" t="s">
-        <v>360</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y34" s="74"/>
+      <c r="Z34" s="74"/>
       <c r="AA34" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB34" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC34" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD34" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD34" s="74"/>
       <c r="AE34" s="74"/>
       <c r="AF34" s="74"/>
     </row>
     <row r="35" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A35" s="97"/>
       <c r="B35" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C35" s="74" t="e" cm="1">
         <f t="array" ref="C35">UPPER(INDEX(_xlfn.TEXTSPLIT($D35, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D35" s="74"/>
+      <c r="D35" s="78"/>
       <c r="E35" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F35" s="74" t="s">
-        <v>504</v>
-      </c>
+      <c r="F35" s="74"/>
       <c r="G35" s="74" t="s">
         <v>464</v>
       </c>
@@ -15386,7 +15089,7 @@
       </c>
       <c r="O35" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dtg-kfk02-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P35" s="74">
         <v>64</v>
@@ -15399,7 +15102,7 @@
       <c r="T35" s="74"/>
       <c r="U35" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dtg-kfk02-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V35" s="74" t="b">
         <v>1</v>
@@ -15408,45 +15111,37 @@
         <v>1</v>
       </c>
       <c r="X35" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y35" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z35" s="74" t="s">
-        <v>360</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y35" s="74"/>
+      <c r="Z35" s="74"/>
       <c r="AA35" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB35" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC35" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD35" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD35" s="74"/>
       <c r="AE35" s="74"/>
       <c r="AF35" s="74"/>
     </row>
     <row r="36" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A36" s="97"/>
       <c r="B36" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C36" s="74" t="e" cm="1">
         <f t="array" ref="C36">UPPER(INDEX(_xlfn.TEXTSPLIT($D36, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D36" s="74"/>
+      <c r="D36" s="88"/>
       <c r="E36" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F36" s="74" t="s">
-        <v>505</v>
-      </c>
+      <c r="F36" s="74"/>
       <c r="G36" s="74" t="s">
         <v>465</v>
       </c>
@@ -15473,7 +15168,7 @@
       </c>
       <c r="O36" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dtg-kfk03-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P36" s="74">
         <v>64</v>
@@ -15486,7 +15181,7 @@
       <c r="T36" s="74"/>
       <c r="U36" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dtg-kfk03-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V36" s="74" t="b">
         <v>1</v>
@@ -15495,45 +15190,37 @@
         <v>1</v>
       </c>
       <c r="X36" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y36" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z36" s="74" t="s">
-        <v>360</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y36" s="74"/>
+      <c r="Z36" s="74"/>
       <c r="AA36" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB36" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC36" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD36" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD36" s="74"/>
       <c r="AE36" s="74"/>
       <c r="AF36" s="74"/>
     </row>
     <row r="37" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A37" s="97"/>
       <c r="B37" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C37" s="74" t="e" cm="1">
         <f t="array" ref="C37">UPPER(INDEX(_xlfn.TEXTSPLIT($D37, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D37" s="74"/>
+      <c r="D37" s="78"/>
       <c r="E37" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F37" s="74" t="s">
-        <v>506</v>
-      </c>
+      <c r="F37" s="74"/>
       <c r="G37" s="74" t="s">
         <v>466</v>
       </c>
@@ -15560,7 +15247,7 @@
       </c>
       <c r="O37" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dtg-mdoms01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P37" s="74">
         <v>64</v>
@@ -15573,7 +15260,7 @@
       <c r="T37" s="74"/>
       <c r="U37" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dtg-mdoms01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V37" s="74" t="b">
         <v>1</v>
@@ -15582,45 +15269,37 @@
         <v>1</v>
       </c>
       <c r="X37" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y37" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z37" s="74" t="s">
-        <v>360</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y37" s="74"/>
+      <c r="Z37" s="74"/>
       <c r="AA37" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB37" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC37" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD37" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD37" s="74"/>
       <c r="AE37" s="74"/>
       <c r="AF37" s="74"/>
     </row>
     <row r="38" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A38" s="97"/>
       <c r="B38" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C38" s="74" t="e" cm="1">
         <f t="array" ref="C38">UPPER(INDEX(_xlfn.TEXTSPLIT($D38, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D38" s="74"/>
+      <c r="D38" s="88"/>
       <c r="E38" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F38" s="74" t="s">
-        <v>507</v>
-      </c>
+      <c r="F38" s="74"/>
       <c r="G38" s="74" t="s">
         <v>370</v>
       </c>
@@ -15647,7 +15326,7 @@
       </c>
       <c r="O38" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dtg-cdmlap01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P38" s="74">
         <v>64</v>
@@ -15660,7 +15339,7 @@
       <c r="T38" s="74"/>
       <c r="U38" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dtg-cdmlap01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V38" s="74" t="b">
         <v>1</v>
@@ -15669,45 +15348,37 @@
         <v>1</v>
       </c>
       <c r="X38" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y38" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z38" s="74" t="s">
-        <v>360</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y38" s="74"/>
+      <c r="Z38" s="74"/>
       <c r="AA38" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB38" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC38" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD38" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD38" s="74"/>
       <c r="AE38" s="74"/>
       <c r="AF38" s="74"/>
     </row>
     <row r="39" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A39" s="97"/>
       <c r="B39" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C39" s="74" t="e" cm="1">
         <f t="array" ref="C39">UPPER(INDEX(_xlfn.TEXTSPLIT($D39, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D39" s="74"/>
+      <c r="D39" s="78"/>
       <c r="E39" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F39" s="74" t="s">
-        <v>508</v>
-      </c>
+      <c r="F39" s="74"/>
       <c r="G39" s="74" t="s">
         <v>371</v>
       </c>
@@ -15734,7 +15405,7 @@
       </c>
       <c r="O39" s="74" t="str">
         <f t="shared" si="2"/>
-        <v>t-dtg-cdstap01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P39" s="74">
         <v>64</v>
@@ -15747,7 +15418,7 @@
       <c r="T39" s="74"/>
       <c r="U39" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dtg-cdstap01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V39" s="74" t="b">
         <v>1</v>
@@ -15756,45 +15427,37 @@
         <v>1</v>
       </c>
       <c r="X39" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y39" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z39" s="74" t="s">
-        <v>360</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y39" s="74"/>
+      <c r="Z39" s="74"/>
       <c r="AA39" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB39" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC39" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD39" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD39" s="74"/>
       <c r="AE39" s="74"/>
       <c r="AF39" s="74"/>
     </row>
     <row r="40" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A40" s="97"/>
       <c r="B40" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C40" s="74" t="e" cm="1">
         <f t="array" ref="C40">UPPER(INDEX(_xlfn.TEXTSPLIT($D40, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D40" s="74"/>
+      <c r="D40" s="88"/>
       <c r="E40" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F40" s="74" t="s">
-        <v>509</v>
-      </c>
+      <c r="F40" s="74"/>
       <c r="G40" s="74" t="s">
         <v>372</v>
       </c>
@@ -15821,7 +15484,7 @@
       </c>
       <c r="O40" s="74" t="str">
         <f t="shared" ref="O40:O64" si="3">SUBSTITUTE(F40,"hazr-","")&amp;"-osdisk"</f>
-        <v>t-dtg-cdsvadm01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P40" s="74">
         <v>64</v>
@@ -15834,7 +15497,7 @@
       <c r="T40" s="74"/>
       <c r="U40" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dtg-cdsvadm01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V40" s="74" t="b">
         <v>1</v>
@@ -15843,45 +15506,37 @@
         <v>1</v>
       </c>
       <c r="X40" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y40" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z40" s="74" t="s">
-        <v>360</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y40" s="74"/>
+      <c r="Z40" s="74"/>
       <c r="AA40" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB40" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC40" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD40" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD40" s="74"/>
       <c r="AE40" s="74"/>
       <c r="AF40" s="74"/>
     </row>
     <row r="41" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A41" s="97"/>
       <c r="B41" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C41" s="74" t="e" cm="1">
         <f t="array" ref="C41">UPPER(INDEX(_xlfn.TEXTSPLIT($D41, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D41" s="74"/>
+      <c r="D41" s="78"/>
       <c r="E41" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F41" s="74" t="s">
-        <v>510</v>
-      </c>
+      <c r="F41" s="74"/>
       <c r="G41" s="74" t="s">
         <v>373</v>
       </c>
@@ -15908,7 +15563,7 @@
       </c>
       <c r="O41" s="74" t="str">
         <f t="shared" si="3"/>
-        <v>t-dtg-diosap01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P41" s="74">
         <v>64</v>
@@ -15921,7 +15576,7 @@
       <c r="T41" s="74"/>
       <c r="U41" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dtg-diosap01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V41" s="74" t="b">
         <v>1</v>
@@ -15930,45 +15585,37 @@
         <v>1</v>
       </c>
       <c r="X41" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y41" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z41" s="74" t="s">
-        <v>360</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y41" s="74"/>
+      <c r="Z41" s="74"/>
       <c r="AA41" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB41" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC41" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD41" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD41" s="74"/>
       <c r="AE41" s="74"/>
       <c r="AF41" s="74"/>
     </row>
     <row r="42" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A42" s="97"/>
       <c r="B42" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C42" s="74" t="e" cm="1">
         <f t="array" ref="C42">UPPER(INDEX(_xlfn.TEXTSPLIT($D42, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D42" s="74"/>
+      <c r="D42" s="88"/>
       <c r="E42" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F42" s="74" t="s">
-        <v>511</v>
-      </c>
+      <c r="F42" s="74"/>
       <c r="G42" s="74" t="s">
         <v>374</v>
       </c>
@@ -15995,7 +15642,7 @@
       </c>
       <c r="O42" s="74" t="str">
         <f t="shared" si="3"/>
-        <v>t-dtg-diosweb01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P42" s="74">
         <v>64</v>
@@ -16008,7 +15655,7 @@
       <c r="T42" s="74"/>
       <c r="U42" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dtg-diosweb01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V42" s="74" t="b">
         <v>1</v>
@@ -16017,45 +15664,37 @@
         <v>1</v>
       </c>
       <c r="X42" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y42" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z42" s="74" t="s">
-        <v>360</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y42" s="74"/>
+      <c r="Z42" s="74"/>
       <c r="AA42" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB42" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC42" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD42" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD42" s="74"/>
       <c r="AE42" s="74"/>
       <c r="AF42" s="74"/>
     </row>
     <row r="43" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A43" s="97"/>
       <c r="B43" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C43" s="74" t="e" cm="1">
         <f t="array" ref="C43">UPPER(INDEX(_xlfn.TEXTSPLIT($D43, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D43" s="74"/>
+      <c r="D43" s="78"/>
       <c r="E43" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F43" s="74" t="s">
-        <v>512</v>
-      </c>
+      <c r="F43" s="74"/>
       <c r="G43" s="74" t="s">
         <v>375</v>
       </c>
@@ -16082,7 +15721,7 @@
       </c>
       <c r="O43" s="74" t="str">
         <f t="shared" si="3"/>
-        <v>t-dtg-dprweb01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P43" s="74">
         <v>64</v>
@@ -16095,7 +15734,7 @@
       <c r="T43" s="74"/>
       <c r="U43" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dtg-dprweb01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V43" s="74" t="b">
         <v>1</v>
@@ -16104,45 +15743,37 @@
         <v>1</v>
       </c>
       <c r="X43" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y43" s="74" t="s">
-        <v>452</v>
-      </c>
-      <c r="Z43" s="74" t="s">
-        <v>365</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y43" s="74"/>
+      <c r="Z43" s="74"/>
       <c r="AA43" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB43" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC43" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD43" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD43" s="74"/>
       <c r="AE43" s="74"/>
       <c r="AF43" s="74"/>
     </row>
     <row r="44" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A44" s="97"/>
       <c r="B44" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C44" s="74" t="e" cm="1">
         <f t="array" ref="C44">UPPER(INDEX(_xlfn.TEXTSPLIT($D44, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D44" s="74"/>
+      <c r="D44" s="88"/>
       <c r="E44" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F44" s="74" t="s">
-        <v>513</v>
-      </c>
+      <c r="F44" s="74"/>
       <c r="G44" s="74" t="s">
         <v>376</v>
       </c>
@@ -16169,7 +15800,7 @@
       </c>
       <c r="O44" s="74" t="str">
         <f t="shared" si="3"/>
-        <v>t-dtg-dprap01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P44" s="74">
         <v>64</v>
@@ -16182,7 +15813,7 @@
       <c r="T44" s="74"/>
       <c r="U44" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dtg-dprap01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V44" s="74" t="b">
         <v>1</v>
@@ -16191,45 +15822,37 @@
         <v>1</v>
       </c>
       <c r="X44" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y44" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z44" s="74" t="s">
-        <v>360</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y44" s="74"/>
+      <c r="Z44" s="74"/>
       <c r="AA44" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB44" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC44" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD44" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD44" s="74"/>
       <c r="AE44" s="74"/>
       <c r="AF44" s="74"/>
     </row>
     <row r="45" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A45" s="97"/>
       <c r="B45" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C45" s="74" t="e" cm="1">
         <f t="array" ref="C45">UPPER(INDEX(_xlfn.TEXTSPLIT($D45, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D45" s="74"/>
+      <c r="D45" s="78"/>
       <c r="E45" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F45" s="74" t="s">
-        <v>514</v>
-      </c>
+      <c r="F45" s="74"/>
       <c r="G45" s="74" t="s">
         <v>378</v>
       </c>
@@ -16256,7 +15879,7 @@
       </c>
       <c r="O45" s="74" t="str">
         <f t="shared" si="3"/>
-        <v>t-bdp-airfw01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P45" s="74">
         <v>64</v>
@@ -16269,7 +15892,7 @@
       <c r="T45" s="74"/>
       <c r="U45" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-bdp-airfw01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V45" s="74" t="b">
         <v>1</v>
@@ -16278,45 +15901,37 @@
         <v>1</v>
       </c>
       <c r="X45" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y45" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z45" s="74" t="s">
-        <v>377</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y45" s="74"/>
+      <c r="Z45" s="74"/>
       <c r="AA45" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB45" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC45" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD45" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD45" s="74"/>
       <c r="AE45" s="74"/>
       <c r="AF45" s="74"/>
     </row>
     <row r="46" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A46" s="97"/>
       <c r="B46" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C46" s="74" t="e" cm="1">
         <f t="array" ref="C46">UPPER(INDEX(_xlfn.TEXTSPLIT($D46, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D46" s="74"/>
+      <c r="D46" s="88"/>
       <c r="E46" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F46" s="74" t="s">
-        <v>515</v>
-      </c>
+      <c r="F46" s="74"/>
       <c r="G46" s="74" t="s">
         <v>467</v>
       </c>
@@ -16343,7 +15958,7 @@
       </c>
       <c r="O46" s="74" t="str">
         <f t="shared" si="3"/>
-        <v>t-bdp-kepler01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P46" s="74">
         <v>64</v>
@@ -16356,7 +15971,7 @@
       <c r="T46" s="74"/>
       <c r="U46" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-bdp-kepler01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V46" s="74" t="b">
         <v>1</v>
@@ -16365,45 +15980,37 @@
         <v>1</v>
       </c>
       <c r="X46" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y46" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z46" s="74" t="s">
-        <v>377</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y46" s="74"/>
+      <c r="Z46" s="74"/>
       <c r="AA46" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB46" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC46" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD46" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD46" s="74"/>
       <c r="AE46" s="74"/>
       <c r="AF46" s="74"/>
     </row>
     <row r="47" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A47" s="97"/>
       <c r="B47" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C47" s="74" t="e" cm="1">
         <f t="array" ref="C47">UPPER(INDEX(_xlfn.TEXTSPLIT($D47, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D47" s="74"/>
+      <c r="D47" s="78"/>
       <c r="E47" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F47" s="74" t="s">
-        <v>516</v>
-      </c>
+      <c r="F47" s="74"/>
       <c r="G47" s="74" t="s">
         <v>379</v>
       </c>
@@ -16430,7 +16037,7 @@
       </c>
       <c r="O47" s="74" t="str">
         <f t="shared" si="3"/>
-        <v>t-bdp-cxmadm01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P47" s="74">
         <v>64</v>
@@ -16443,7 +16050,7 @@
       <c r="T47" s="74"/>
       <c r="U47" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-bdp-cxmadm01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V47" s="74" t="b">
         <v>1</v>
@@ -16452,45 +16059,37 @@
         <v>1</v>
       </c>
       <c r="X47" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y47" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z47" s="74" t="s">
-        <v>377</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y47" s="74"/>
+      <c r="Z47" s="74"/>
       <c r="AA47" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB47" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC47" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD47" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD47" s="74"/>
       <c r="AE47" s="74"/>
       <c r="AF47" s="74"/>
     </row>
     <row r="48" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A48" s="97"/>
       <c r="B48" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C48" s="74" t="e" cm="1">
         <f t="array" ref="C48">UPPER(INDEX(_xlfn.TEXTSPLIT($D48, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D48" s="74"/>
+      <c r="D48" s="88"/>
       <c r="E48" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F48" s="74" t="s">
-        <v>517</v>
-      </c>
+      <c r="F48" s="74"/>
       <c r="G48" s="74" t="s">
         <v>380</v>
       </c>
@@ -16517,7 +16116,7 @@
       </c>
       <c r="O48" s="74" t="str">
         <f t="shared" si="3"/>
-        <v>t-bdp-slap01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P48" s="74">
         <v>64</v>
@@ -16530,7 +16129,7 @@
       <c r="T48" s="74"/>
       <c r="U48" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-bdp-slap01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V48" s="74" t="b">
         <v>1</v>
@@ -16539,45 +16138,37 @@
         <v>1</v>
       </c>
       <c r="X48" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y48" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z48" s="74" t="s">
-        <v>377</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y48" s="74"/>
+      <c r="Z48" s="74"/>
       <c r="AA48" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB48" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC48" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD48" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD48" s="74"/>
       <c r="AE48" s="74"/>
       <c r="AF48" s="74"/>
     </row>
     <row r="49" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A49" s="97"/>
       <c r="B49" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C49" s="74" t="e" cm="1">
         <f t="array" ref="C49">UPPER(INDEX(_xlfn.TEXTSPLIT($D49, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D49" s="74"/>
+      <c r="D49" s="78"/>
       <c r="E49" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F49" s="74" t="s">
-        <v>518</v>
-      </c>
+      <c r="F49" s="74"/>
       <c r="G49" s="74" t="s">
         <v>382</v>
       </c>
@@ -16604,7 +16195,7 @@
       </c>
       <c r="O49" s="74" t="str">
         <f t="shared" si="3"/>
-        <v>t-dip-adm01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P49" s="74">
         <v>64</v>
@@ -16617,7 +16208,7 @@
       <c r="T49" s="74"/>
       <c r="U49" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dip-adm01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V49" s="74" t="b">
         <v>1</v>
@@ -16626,45 +16217,37 @@
         <v>1</v>
       </c>
       <c r="X49" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y49" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z49" s="74" t="s">
-        <v>381</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y49" s="74"/>
+      <c r="Z49" s="74"/>
       <c r="AA49" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB49" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC49" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD49" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD49" s="74"/>
       <c r="AE49" s="74"/>
       <c r="AF49" s="74"/>
     </row>
     <row r="50" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A50" s="97"/>
       <c r="B50" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C50" s="74" t="e" cm="1">
         <f t="array" ref="C50">UPPER(INDEX(_xlfn.TEXTSPLIT($D50, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D50" s="74"/>
+      <c r="D50" s="88"/>
       <c r="E50" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F50" s="74" t="s">
-        <v>519</v>
-      </c>
+      <c r="F50" s="74"/>
       <c r="G50" s="74" t="s">
         <v>383</v>
       </c>
@@ -16691,7 +16274,7 @@
       </c>
       <c r="O50" s="74" t="str">
         <f t="shared" si="3"/>
-        <v>t-dip-ap01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P50" s="74">
         <v>64</v>
@@ -16704,7 +16287,7 @@
       <c r="T50" s="74"/>
       <c r="U50" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dip-ap01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V50" s="74" t="b">
         <v>1</v>
@@ -16713,45 +16296,37 @@
         <v>1</v>
       </c>
       <c r="X50" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y50" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z50" s="74" t="s">
-        <v>381</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y50" s="74"/>
+      <c r="Z50" s="74"/>
       <c r="AA50" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB50" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC50" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD50" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD50" s="74"/>
       <c r="AE50" s="74"/>
       <c r="AF50" s="74"/>
     </row>
     <row r="51" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A51" s="97"/>
       <c r="B51" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C51" s="74" t="e" cm="1">
         <f t="array" ref="C51">UPPER(INDEX(_xlfn.TEXTSPLIT($D51, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D51" s="74"/>
+      <c r="D51" s="78"/>
       <c r="E51" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F51" s="74" t="s">
-        <v>520</v>
-      </c>
+      <c r="F51" s="74"/>
       <c r="G51" s="74" t="s">
         <v>384</v>
       </c>
@@ -16778,7 +16353,7 @@
       </c>
       <c r="O51" s="74" t="str">
         <f t="shared" si="3"/>
-        <v>t-dip-flk01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P51" s="74">
         <v>64</v>
@@ -16791,7 +16366,7 @@
       <c r="T51" s="74"/>
       <c r="U51" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dip-flk01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V51" s="74" t="b">
         <v>1</v>
@@ -16800,45 +16375,37 @@
         <v>1</v>
       </c>
       <c r="X51" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y51" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z51" s="74" t="s">
-        <v>381</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y51" s="74"/>
+      <c r="Z51" s="74"/>
       <c r="AA51" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB51" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC51" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD51" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD51" s="74"/>
       <c r="AE51" s="74"/>
       <c r="AF51" s="74"/>
     </row>
     <row r="52" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A52" s="97"/>
       <c r="B52" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C52" s="74" t="e" cm="1">
         <f t="array" ref="C52">UPPER(INDEX(_xlfn.TEXTSPLIT($D52, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D52" s="74"/>
+      <c r="D52" s="88"/>
       <c r="E52" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F52" s="74" t="s">
-        <v>521</v>
-      </c>
+      <c r="F52" s="74"/>
       <c r="G52" s="74" t="s">
         <v>385</v>
       </c>
@@ -16865,7 +16432,7 @@
       </c>
       <c r="O52" s="74" t="str">
         <f t="shared" si="3"/>
-        <v>t-dip-flk02-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P52" s="74">
         <v>64</v>
@@ -16878,7 +16445,7 @@
       <c r="T52" s="74"/>
       <c r="U52" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dip-flk02-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V52" s="74" t="b">
         <v>1</v>
@@ -16887,45 +16454,37 @@
         <v>1</v>
       </c>
       <c r="X52" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y52" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z52" s="74" t="s">
-        <v>381</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y52" s="74"/>
+      <c r="Z52" s="74"/>
       <c r="AA52" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB52" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC52" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD52" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD52" s="74"/>
       <c r="AE52" s="74"/>
       <c r="AF52" s="74"/>
     </row>
     <row r="53" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A53" s="97"/>
       <c r="B53" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C53" s="74" t="e" cm="1">
         <f t="array" ref="C53">UPPER(INDEX(_xlfn.TEXTSPLIT($D53, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D53" s="74"/>
+      <c r="D53" s="78"/>
       <c r="E53" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F53" s="74" t="s">
-        <v>522</v>
-      </c>
+      <c r="F53" s="74"/>
       <c r="G53" s="74" t="s">
         <v>386</v>
       </c>
@@ -16952,7 +16511,7 @@
       </c>
       <c r="O53" s="74" t="str">
         <f t="shared" si="3"/>
-        <v>t-dip-flk03-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P53" s="74">
         <v>64</v>
@@ -16965,7 +16524,7 @@
       <c r="T53" s="74"/>
       <c r="U53" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dip-flk03-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V53" s="74" t="b">
         <v>1</v>
@@ -16974,45 +16533,37 @@
         <v>1</v>
       </c>
       <c r="X53" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y53" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z53" s="74" t="s">
-        <v>381</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y53" s="74"/>
+      <c r="Z53" s="74"/>
       <c r="AA53" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB53" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC53" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD53" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD53" s="74"/>
       <c r="AE53" s="74"/>
       <c r="AF53" s="74"/>
     </row>
     <row r="54" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A54" s="97"/>
       <c r="B54" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C54" s="74" t="e" cm="1">
         <f t="array" ref="C54">UPPER(INDEX(_xlfn.TEXTSPLIT($D54, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D54" s="74"/>
+      <c r="D54" s="88"/>
       <c r="E54" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F54" s="74" t="s">
-        <v>523</v>
-      </c>
+      <c r="F54" s="74"/>
       <c r="G54" s="74" t="s">
         <v>387</v>
       </c>
@@ -17039,7 +16590,7 @@
       </c>
       <c r="O54" s="74" t="str">
         <f t="shared" si="3"/>
-        <v>t-dip-geoap01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P54" s="74">
         <v>64</v>
@@ -17052,7 +16603,7 @@
       <c r="T54" s="74"/>
       <c r="U54" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dip-geoap01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V54" s="74" t="b">
         <v>1</v>
@@ -17061,45 +16612,37 @@
         <v>1</v>
       </c>
       <c r="X54" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y54" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z54" s="74" t="s">
-        <v>381</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y54" s="74"/>
+      <c r="Z54" s="74"/>
       <c r="AA54" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB54" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC54" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD54" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD54" s="74"/>
       <c r="AE54" s="74"/>
       <c r="AF54" s="74"/>
     </row>
     <row r="55" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A55" s="97"/>
       <c r="B55" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C55" s="74" t="e" cm="1">
         <f t="array" ref="C55">UPPER(INDEX(_xlfn.TEXTSPLIT($D55, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D55" s="74"/>
+      <c r="D55" s="78"/>
       <c r="E55" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F55" s="74" t="s">
-        <v>524</v>
-      </c>
+      <c r="F55" s="74"/>
       <c r="G55" s="74" t="s">
         <v>468</v>
       </c>
@@ -17126,7 +16669,7 @@
       </c>
       <c r="O55" s="74" t="str">
         <f t="shared" si="3"/>
-        <v>t-dip-kfk01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P55" s="74">
         <v>64</v>
@@ -17139,7 +16682,7 @@
       <c r="T55" s="74"/>
       <c r="U55" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dip-kfk01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V55" s="74" t="b">
         <v>1</v>
@@ -17148,45 +16691,37 @@
         <v>1</v>
       </c>
       <c r="X55" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y55" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z55" s="74" t="s">
-        <v>381</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y55" s="74"/>
+      <c r="Z55" s="74"/>
       <c r="AA55" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB55" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC55" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD55" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD55" s="74"/>
       <c r="AE55" s="74"/>
       <c r="AF55" s="74"/>
     </row>
     <row r="56" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A56" s="97"/>
       <c r="B56" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C56" s="74" t="e" cm="1">
         <f t="array" ref="C56">UPPER(INDEX(_xlfn.TEXTSPLIT($D56, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D56" s="74"/>
+      <c r="D56" s="88"/>
       <c r="E56" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F56" s="74" t="s">
-        <v>525</v>
-      </c>
+      <c r="F56" s="74"/>
       <c r="G56" s="74" t="s">
         <v>469</v>
       </c>
@@ -17213,7 +16748,7 @@
       </c>
       <c r="O56" s="74" t="str">
         <f t="shared" si="3"/>
-        <v>t-dip-kfk02-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P56" s="74">
         <v>64</v>
@@ -17226,7 +16761,7 @@
       <c r="T56" s="74"/>
       <c r="U56" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dip-kfk02-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V56" s="74" t="b">
         <v>1</v>
@@ -17235,45 +16770,37 @@
         <v>1</v>
       </c>
       <c r="X56" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y56" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z56" s="74" t="s">
-        <v>381</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y56" s="74"/>
+      <c r="Z56" s="74"/>
       <c r="AA56" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB56" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC56" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD56" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD56" s="74"/>
       <c r="AE56" s="74"/>
       <c r="AF56" s="74"/>
     </row>
     <row r="57" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A57" s="97"/>
       <c r="B57" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C57" s="74" t="e" cm="1">
         <f t="array" ref="C57">UPPER(INDEX(_xlfn.TEXTSPLIT($D57, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D57" s="74"/>
+      <c r="D57" s="78"/>
       <c r="E57" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F57" s="74" t="s">
-        <v>526</v>
-      </c>
+      <c r="F57" s="74"/>
       <c r="G57" s="74" t="s">
         <v>470</v>
       </c>
@@ -17300,7 +16827,7 @@
       </c>
       <c r="O57" s="74" t="str">
         <f t="shared" si="3"/>
-        <v>t-dip-kfk03-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P57" s="74">
         <v>64</v>
@@ -17313,7 +16840,7 @@
       <c r="T57" s="74"/>
       <c r="U57" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dip-kfk03-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V57" s="74" t="b">
         <v>1</v>
@@ -17322,45 +16849,37 @@
         <v>1</v>
       </c>
       <c r="X57" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y57" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z57" s="74" t="s">
-        <v>381</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y57" s="74"/>
+      <c r="Z57" s="74"/>
       <c r="AA57" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB57" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC57" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD57" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD57" s="74"/>
       <c r="AE57" s="74"/>
       <c r="AF57" s="74"/>
     </row>
     <row r="58" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A58" s="97"/>
       <c r="B58" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C58" s="74" t="e" cm="1">
         <f t="array" ref="C58">UPPER(INDEX(_xlfn.TEXTSPLIT($D58, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D58" s="74"/>
+      <c r="D58" s="88"/>
       <c r="E58" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F58" s="74" t="s">
-        <v>527</v>
-      </c>
+      <c r="F58" s="74"/>
       <c r="G58" s="74" t="s">
         <v>388</v>
       </c>
@@ -17387,7 +16906,7 @@
       </c>
       <c r="O58" s="74" t="str">
         <f t="shared" si="3"/>
-        <v>t-dip-mqap01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P58" s="74">
         <v>64</v>
@@ -17400,7 +16919,7 @@
       <c r="T58" s="74"/>
       <c r="U58" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dip-mqap01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V58" s="74" t="b">
         <v>1</v>
@@ -17409,45 +16928,37 @@
         <v>1</v>
       </c>
       <c r="X58" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y58" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z58" s="74" t="s">
-        <v>381</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y58" s="74"/>
+      <c r="Z58" s="74"/>
       <c r="AA58" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB58" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC58" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD58" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD58" s="74"/>
       <c r="AE58" s="74"/>
       <c r="AF58" s="74"/>
     </row>
     <row r="59" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A59" s="97"/>
       <c r="B59" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C59" s="74" t="e" cm="1">
         <f t="array" ref="C59">UPPER(INDEX(_xlfn.TEXTSPLIT($D59, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D59" s="74"/>
+      <c r="D59" s="78"/>
       <c r="E59" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F59" s="74" t="s">
-        <v>528</v>
-      </c>
+      <c r="F59" s="74"/>
       <c r="G59" s="74" t="s">
         <v>389</v>
       </c>
@@ -17474,7 +16985,7 @@
       </c>
       <c r="O59" s="74" t="str">
         <f t="shared" si="3"/>
-        <v>t-dip-mqweb01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P59" s="74">
         <v>64</v>
@@ -17487,7 +16998,7 @@
       <c r="T59" s="74"/>
       <c r="U59" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dip-mqweb01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V59" s="74" t="b">
         <v>1</v>
@@ -17496,45 +17007,37 @@
         <v>1</v>
       </c>
       <c r="X59" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y59" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z59" s="74" t="s">
-        <v>381</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y59" s="74"/>
+      <c r="Z59" s="74"/>
       <c r="AA59" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB59" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC59" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD59" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD59" s="74"/>
       <c r="AE59" s="74"/>
       <c r="AF59" s="74"/>
     </row>
     <row r="60" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A60" s="97"/>
       <c r="B60" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C60" s="74" t="e" cm="1">
         <f t="array" ref="C60">UPPER(INDEX(_xlfn.TEXTSPLIT($D60, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D60" s="74"/>
+      <c r="D60" s="88"/>
       <c r="E60" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F60" s="74" t="s">
-        <v>529</v>
-      </c>
+      <c r="F60" s="74"/>
       <c r="G60" s="74" t="s">
         <v>471</v>
       </c>
@@ -17561,7 +17064,7 @@
       </c>
       <c r="O60" s="74" t="str">
         <f t="shared" si="3"/>
-        <v>t-dip-oms01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P60" s="74">
         <v>64</v>
@@ -17574,7 +17077,7 @@
       <c r="T60" s="74"/>
       <c r="U60" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dip-oms01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V60" s="74" t="b">
         <v>1</v>
@@ -17583,45 +17086,37 @@
         <v>1</v>
       </c>
       <c r="X60" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y60" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z60" s="74" t="s">
-        <v>381</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y60" s="74"/>
+      <c r="Z60" s="74"/>
       <c r="AA60" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB60" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC60" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD60" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD60" s="74"/>
       <c r="AE60" s="74"/>
       <c r="AF60" s="74"/>
     </row>
     <row r="61" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A61" s="97"/>
       <c r="B61" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C61" s="74" t="e" cm="1">
         <f t="array" ref="C61">UPPER(INDEX(_xlfn.TEXTSPLIT($D61, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D61" s="74"/>
+      <c r="D61" s="78"/>
       <c r="E61" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F61" s="74" t="s">
-        <v>530</v>
-      </c>
+      <c r="F61" s="74"/>
       <c r="G61" s="74" t="s">
         <v>390</v>
       </c>
@@ -17648,7 +17143,7 @@
       </c>
       <c r="O61" s="74" t="str">
         <f t="shared" si="3"/>
-        <v>t-dip-web01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P61" s="74">
         <v>64</v>
@@ -17661,7 +17156,7 @@
       <c r="T61" s="74"/>
       <c r="U61" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-dip-web01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V61" s="74" t="b">
         <v>1</v>
@@ -17670,45 +17165,37 @@
         <v>1</v>
       </c>
       <c r="X61" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y61" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z61" s="74" t="s">
-        <v>381</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y61" s="74"/>
+      <c r="Z61" s="74"/>
       <c r="AA61" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB61" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC61" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD61" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD61" s="74"/>
       <c r="AE61" s="74"/>
       <c r="AF61" s="74"/>
     </row>
     <row r="62" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A62" s="97"/>
       <c r="B62" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C62" s="74" t="e" cm="1">
         <f t="array" ref="C62">UPPER(INDEX(_xlfn.TEXTSPLIT($D62, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D62" s="74"/>
+      <c r="D62" s="88"/>
       <c r="E62" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F62" s="74" t="s">
-        <v>531</v>
-      </c>
+      <c r="F62" s="74"/>
       <c r="G62" s="74" t="s">
         <v>392</v>
       </c>
@@ -17735,7 +17222,7 @@
       </c>
       <c r="O62" s="74" t="str">
         <f t="shared" si="3"/>
-        <v>t-com-auth01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P62" s="74">
         <v>64</v>
@@ -17748,7 +17235,7 @@
       <c r="T62" s="74"/>
       <c r="U62" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-com-auth01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V62" s="74" t="b">
         <v>1</v>
@@ -17757,45 +17244,37 @@
         <v>1</v>
       </c>
       <c r="X62" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y62" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z62" s="74" t="s">
-        <v>391</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y62" s="74"/>
+      <c r="Z62" s="74"/>
       <c r="AA62" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB62" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC62" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD62" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD62" s="74"/>
       <c r="AE62" s="74"/>
       <c r="AF62" s="74"/>
     </row>
     <row r="63" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A63" s="97"/>
       <c r="B63" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C63" s="74" t="e" cm="1">
         <f t="array" ref="C63">UPPER(INDEX(_xlfn.TEXTSPLIT($D63, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D63" s="74"/>
+      <c r="D63" s="78"/>
       <c r="E63" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F63" s="74" t="s">
-        <v>532</v>
-      </c>
+      <c r="F63" s="74"/>
       <c r="G63" s="74" t="s">
         <v>394</v>
       </c>
@@ -17822,7 +17301,7 @@
       </c>
       <c r="O63" s="74" t="str">
         <f t="shared" si="3"/>
-        <v>t-com-proxy01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P63" s="74">
         <v>64</v>
@@ -17835,7 +17314,7 @@
       <c r="T63" s="74"/>
       <c r="U63" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-com-proxy01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V63" s="74" t="b">
         <v>1</v>
@@ -17844,45 +17323,37 @@
         <v>1</v>
       </c>
       <c r="X63" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y63" s="74" t="s">
-        <v>452</v>
-      </c>
-      <c r="Z63" s="74" t="s">
-        <v>393</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y63" s="74"/>
+      <c r="Z63" s="74"/>
       <c r="AA63" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB63" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC63" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD63" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD63" s="74"/>
       <c r="AE63" s="74"/>
       <c r="AF63" s="74"/>
     </row>
     <row r="64" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A64" s="97"/>
       <c r="B64" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C64" s="74" t="e" cm="1">
         <f t="array" ref="C64">UPPER(INDEX(_xlfn.TEXTSPLIT($D64, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D64" s="74"/>
+      <c r="D64" s="88"/>
       <c r="E64" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F64" s="74" t="s">
-        <v>533</v>
-      </c>
+      <c r="F64" s="74"/>
       <c r="G64" s="74" t="s">
         <v>473</v>
       </c>
@@ -17909,7 +17380,7 @@
       </c>
       <c r="O64" s="74" t="str">
         <f t="shared" si="3"/>
-        <v>t-if-gramon01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P64" s="74">
         <v>64</v>
@@ -17922,7 +17393,7 @@
       <c r="T64" s="74"/>
       <c r="U64" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-if-gramon01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V64" s="74" t="b">
         <v>1</v>
@@ -17931,45 +17402,37 @@
         <v>1</v>
       </c>
       <c r="X64" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y64" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z64" s="74" t="s">
-        <v>472</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y64" s="74"/>
+      <c r="Z64" s="74"/>
       <c r="AA64" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB64" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC64" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD64" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD64" s="74"/>
       <c r="AE64" s="74"/>
       <c r="AF64" s="74"/>
     </row>
     <row r="65" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A65" s="97"/>
       <c r="B65" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C65" s="74" t="e" cm="1">
         <f t="array" ref="C65">UPPER(INDEX(_xlfn.TEXTSPLIT($D65, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D65" s="74"/>
+      <c r="D65" s="78"/>
       <c r="E65" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F65" s="74" t="s">
-        <v>534</v>
-      </c>
+      <c r="F65" s="74"/>
       <c r="G65" s="74" t="s">
         <v>396</v>
       </c>
@@ -17996,7 +17459,7 @@
       </c>
       <c r="O65" s="74" t="str">
         <f t="shared" ref="O65:O70" si="4">SUBSTITUTE(F65,"hazr-","")&amp;"-osdisk"</f>
-        <v>t-doip-web01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P65" s="74">
         <v>64</v>
@@ -18009,7 +17472,7 @@
       <c r="T65" s="74"/>
       <c r="U65" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-doip-web01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V65" s="74" t="b">
         <v>1</v>
@@ -18018,45 +17481,37 @@
         <v>1</v>
       </c>
       <c r="X65" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y65" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z65" s="74" t="s">
-        <v>395</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y65" s="74"/>
+      <c r="Z65" s="74"/>
       <c r="AA65" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB65" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC65" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD65" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD65" s="74"/>
       <c r="AE65" s="74"/>
       <c r="AF65" s="74"/>
     </row>
     <row r="66" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A66" s="97"/>
       <c r="B66" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C66" s="74" t="e" cm="1">
         <f t="array" ref="C66">UPPER(INDEX(_xlfn.TEXTSPLIT($D66, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D66" s="74"/>
+      <c r="D66" s="88"/>
       <c r="E66" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F66" s="74" t="s">
-        <v>535</v>
-      </c>
+      <c r="F66" s="74"/>
       <c r="G66" s="74" t="s">
         <v>397</v>
       </c>
@@ -18083,7 +17538,7 @@
       </c>
       <c r="O66" s="74" t="str">
         <f t="shared" si="4"/>
-        <v>t-doip-ap01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P66" s="74">
         <v>64</v>
@@ -18096,7 +17551,7 @@
       <c r="T66" s="74"/>
       <c r="U66" s="74" t="str">
         <f t="shared" si="1"/>
-        <v>t-doip-ap01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V66" s="74" t="b">
         <v>1</v>
@@ -18105,45 +17560,37 @@
         <v>1</v>
       </c>
       <c r="X66" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y66" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z66" s="74" t="s">
-        <v>395</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y66" s="74"/>
+      <c r="Z66" s="74"/>
       <c r="AA66" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB66" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC66" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD66" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD66" s="74"/>
       <c r="AE66" s="74"/>
       <c r="AF66" s="74"/>
     </row>
     <row r="67" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A67" s="97"/>
       <c r="B67" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C67" s="74" t="e" cm="1">
         <f t="array" ref="C67">UPPER(INDEX(_xlfn.TEXTSPLIT($D67, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D67" s="74"/>
+      <c r="D67" s="78"/>
       <c r="E67" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F67" s="74" t="s">
-        <v>536</v>
-      </c>
+      <c r="F67" s="74"/>
       <c r="G67" s="74" t="s">
         <v>398</v>
       </c>
@@ -18170,7 +17617,7 @@
       </c>
       <c r="O67" s="74" t="str">
         <f t="shared" si="4"/>
-        <v>t-doip-adm01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P67" s="74">
         <v>64</v>
@@ -18182,8 +17629,8 @@
       <c r="S67" s="74"/>
       <c r="T67" s="74"/>
       <c r="U67" s="74" t="str">
-        <f t="shared" ref="U67:U72" si="5">SUBSTITUTE(F67,"hazr-","")&amp;"-nic"</f>
-        <v>t-doip-adm01-nic</v>
+        <f t="shared" ref="U67:U70" si="5">SUBSTITUTE(F67,"hazr-","")&amp;"-nic"</f>
+        <v>-nic</v>
       </c>
       <c r="V67" s="74" t="b">
         <v>1</v>
@@ -18192,45 +17639,37 @@
         <v>1</v>
       </c>
       <c r="X67" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y67" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z67" s="74" t="s">
-        <v>395</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y67" s="74"/>
+      <c r="Z67" s="74"/>
       <c r="AA67" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB67" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC67" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD67" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD67" s="74"/>
       <c r="AE67" s="74"/>
       <c r="AF67" s="74"/>
     </row>
     <row r="68" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A68" s="97"/>
       <c r="B68" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C68" s="74" t="e" cm="1">
         <f t="array" ref="C68">UPPER(INDEX(_xlfn.TEXTSPLIT($D68, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D68" s="74"/>
+      <c r="D68" s="88"/>
       <c r="E68" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F68" s="74" t="s">
-        <v>537</v>
-      </c>
+      <c r="F68" s="74"/>
       <c r="G68" s="74" t="s">
         <v>400</v>
       </c>
@@ -18257,7 +17696,7 @@
       </c>
       <c r="O68" s="74" t="str">
         <f t="shared" si="4"/>
-        <v>t-bdp-crkweb01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P68" s="74">
         <v>64</v>
@@ -18270,7 +17709,7 @@
       <c r="T68" s="74"/>
       <c r="U68" s="74" t="str">
         <f t="shared" si="5"/>
-        <v>t-bdp-crkweb01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V68" s="74" t="b">
         <v>1</v>
@@ -18279,45 +17718,37 @@
         <v>1</v>
       </c>
       <c r="X68" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y68" s="74" t="s">
-        <v>452</v>
-      </c>
-      <c r="Z68" s="74" t="s">
-        <v>399</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y68" s="74"/>
+      <c r="Z68" s="74"/>
       <c r="AA68" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB68" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC68" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD68" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD68" s="74"/>
       <c r="AE68" s="74"/>
       <c r="AF68" s="74"/>
     </row>
     <row r="69" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A69" s="97"/>
       <c r="B69" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C69" s="74" t="e" cm="1">
         <f t="array" ref="C69">UPPER(INDEX(_xlfn.TEXTSPLIT($D69, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D69" s="74"/>
+      <c r="D69" s="78"/>
       <c r="E69" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F69" s="74" t="s">
-        <v>538</v>
-      </c>
+      <c r="F69" s="74"/>
       <c r="G69" s="74" t="s">
         <v>401</v>
       </c>
@@ -18344,7 +17775,7 @@
       </c>
       <c r="O69" s="74" t="str">
         <f t="shared" si="4"/>
-        <v>t-bdp-crkap01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P69" s="74">
         <v>64</v>
@@ -18357,7 +17788,7 @@
       <c r="T69" s="74"/>
       <c r="U69" s="74" t="str">
         <f t="shared" si="5"/>
-        <v>t-bdp-crkap01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V69" s="74" t="b">
         <v>1</v>
@@ -18366,45 +17797,37 @@
         <v>1</v>
       </c>
       <c r="X69" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y69" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z69" s="74" t="s">
-        <v>377</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y69" s="74"/>
+      <c r="Z69" s="74"/>
       <c r="AA69" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB69" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC69" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD69" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD69" s="74"/>
       <c r="AE69" s="74"/>
       <c r="AF69" s="74"/>
     </row>
     <row r="70" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A70" s="97"/>
       <c r="B70" s="74" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="C70" s="74" t="e" cm="1">
         <f t="array" ref="C70">UPPER(INDEX(_xlfn.TEXTSPLIT($D70, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D70" s="74"/>
+      <c r="D70" s="88"/>
       <c r="E70" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F70" s="74" t="s">
-        <v>539</v>
-      </c>
+      <c r="F70" s="74"/>
       <c r="G70" s="74" t="s">
         <v>402</v>
       </c>
@@ -18431,7 +17854,7 @@
       </c>
       <c r="O70" s="74" t="str">
         <f t="shared" si="4"/>
-        <v>t-bdp-crkml01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P70" s="74">
         <v>64</v>
@@ -18444,7 +17867,7 @@
       <c r="T70" s="74"/>
       <c r="U70" s="74" t="str">
         <f t="shared" si="5"/>
-        <v>t-bdp-crkml01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V70" s="74" t="b">
         <v>1</v>
@@ -18453,285 +17876,22 @@
         <v>1</v>
       </c>
       <c r="X70" s="74" t="s">
-        <v>200</v>
-      </c>
-      <c r="Y70" s="74" t="s">
-        <v>451</v>
-      </c>
-      <c r="Z70" s="74" t="s">
-        <v>377</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="Y70" s="74"/>
+      <c r="Z70" s="74"/>
       <c r="AA70" s="74" t="b">
         <v>1</v>
       </c>
       <c r="AB70" s="74" t="s">
-        <v>200</v>
+        <v>660</v>
       </c>
       <c r="AC70" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD70" s="74">
-        <v>3</v>
-      </c>
+        <v>661</v>
+      </c>
+      <c r="AD70" s="74"/>
       <c r="AE70" s="74"/>
       <c r="AF70" s="74"/>
-    </row>
-    <row r="71" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B71" s="74" t="s">
-        <v>567</v>
-      </c>
-      <c r="C71" s="74" t="e" cm="1">
-        <f t="array" ref="C71">UPPER(INDEX(_xlfn.TEXTSPLIT($D71, "-"), 3))</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D71" s="74"/>
-      <c r="E71" s="74" t="s">
-        <v>24</v>
-      </c>
-      <c r="F71" s="74" t="s">
-        <v>560</v>
-      </c>
-      <c r="G71" s="74" t="s">
-        <v>556</v>
-      </c>
-      <c r="H71" s="105" t="s">
-        <v>555</v>
-      </c>
-      <c r="I71" s="74">
-        <v>8</v>
-      </c>
-      <c r="J71" s="74">
-        <v>32</v>
-      </c>
-      <c r="K71" s="74" t="s">
-        <v>185</v>
-      </c>
-      <c r="L71" s="106" t="s">
-        <v>542</v>
-      </c>
-      <c r="M71" s="106" t="s">
-        <v>554</v>
-      </c>
-      <c r="N71" s="74" t="s">
-        <v>552</v>
-      </c>
-      <c r="O71" s="74" t="str">
-        <f>SUBSTITUTE(F71,"hazr-","")&amp;"-osdisk"</f>
-        <v>l-mon-whtap01-osdisk</v>
-      </c>
-      <c r="P71" s="74">
-        <v>64</v>
-      </c>
-      <c r="Q71" s="74" t="s">
-        <v>183</v>
-      </c>
-      <c r="R71" s="74"/>
-      <c r="S71" s="74"/>
-      <c r="T71" s="74"/>
-      <c r="U71" s="74" t="str">
-        <f t="shared" si="5"/>
-        <v>l-mon-whtap01-nic</v>
-      </c>
-      <c r="V71" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="W71" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="X71" s="74" t="s">
-        <v>561</v>
-      </c>
-      <c r="Y71" s="74" t="s">
-        <v>259</v>
-      </c>
-      <c r="Z71" s="74" t="s">
-        <v>558</v>
-      </c>
-      <c r="AA71" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB71" s="74" t="s">
-        <v>561</v>
-      </c>
-      <c r="AC71" s="74" t="s">
-        <v>566</v>
-      </c>
-      <c r="AD71" s="74">
-        <v>1</v>
-      </c>
-      <c r="AE71" s="74"/>
-      <c r="AF71" s="74"/>
-    </row>
-    <row r="72" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B72" s="74" t="s">
-        <v>567</v>
-      </c>
-      <c r="C72" s="74" t="e" cm="1">
-        <f t="array" ref="C72">UPPER(INDEX(_xlfn.TEXTSPLIT($D72, "-"), 3))</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D72" s="74"/>
-      <c r="E72" s="74" t="s">
-        <v>24</v>
-      </c>
-      <c r="F72" s="74" t="s">
-        <v>559</v>
-      </c>
-      <c r="G72" s="74" t="s">
-        <v>557</v>
-      </c>
-      <c r="H72" s="105" t="s">
-        <v>555</v>
-      </c>
-      <c r="I72" s="74">
-        <v>8</v>
-      </c>
-      <c r="J72" s="74">
-        <v>32</v>
-      </c>
-      <c r="K72" s="74" t="s">
-        <v>185</v>
-      </c>
-      <c r="L72" s="74" t="s">
-        <v>542</v>
-      </c>
-      <c r="M72" s="106" t="s">
-        <v>554</v>
-      </c>
-      <c r="N72" s="74" t="s">
-        <v>552</v>
-      </c>
-      <c r="O72" s="74" t="str">
-        <f>SUBSTITUTE(F72,"hazr-","")&amp;"-osdisk"</f>
-        <v>l-mon-whtap02-osdisk</v>
-      </c>
-      <c r="P72" s="74">
-        <v>64</v>
-      </c>
-      <c r="Q72" s="74" t="s">
-        <v>183</v>
-      </c>
-      <c r="R72" s="74"/>
-      <c r="S72" s="74"/>
-      <c r="T72" s="74"/>
-      <c r="U72" s="74" t="str">
-        <f t="shared" si="5"/>
-        <v>l-mon-whtap02-nic</v>
-      </c>
-      <c r="V72" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="W72" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="X72" s="74" t="s">
-        <v>561</v>
-      </c>
-      <c r="Y72" s="74" t="s">
-        <v>259</v>
-      </c>
-      <c r="Z72" s="74" t="s">
-        <v>558</v>
-      </c>
-      <c r="AA72" s="74" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB72" s="73" t="s">
-        <v>561</v>
-      </c>
-      <c r="AC72" s="73" t="s">
-        <v>565</v>
-      </c>
-      <c r="AD72" s="74">
-        <v>2</v>
-      </c>
-      <c r="AE72" s="74"/>
-      <c r="AF72" s="74"/>
-    </row>
-    <row r="73" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B73" s="107" t="s">
-        <v>567</v>
-      </c>
-      <c r="C73" s="107" t="s">
-        <v>562</v>
-      </c>
-      <c r="D73" s="107"/>
-      <c r="E73" s="107" t="s">
-        <v>24</v>
-      </c>
-      <c r="F73" s="107" t="s">
-        <v>570</v>
-      </c>
-      <c r="G73" s="107" t="s">
-        <v>571</v>
-      </c>
-      <c r="H73" s="108" t="s">
-        <v>181</v>
-      </c>
-      <c r="I73" s="107">
-        <v>2</v>
-      </c>
-      <c r="J73" s="107">
-        <v>8</v>
-      </c>
-      <c r="K73" s="107" t="s">
-        <v>185</v>
-      </c>
-      <c r="L73" s="109" t="s">
-        <v>180</v>
-      </c>
-      <c r="M73" s="109" t="s">
-        <v>554</v>
-      </c>
-      <c r="N73" s="74" t="s">
-        <v>552</v>
-      </c>
-      <c r="O73" s="107" t="str">
-        <f>SUBSTITUTE(F73,"hazr-","")&amp;"-osdisk"</f>
-        <v>l-mon-whtap03-osdisk</v>
-      </c>
-      <c r="P73" s="107">
-        <v>64</v>
-      </c>
-      <c r="Q73" s="107" t="s">
-        <v>183</v>
-      </c>
-      <c r="R73" s="107"/>
-      <c r="S73" s="107"/>
-      <c r="T73" s="107"/>
-      <c r="U73" s="107" t="str">
-        <f>SUBSTITUTE(F73,"hazr-","")&amp;"-nic"</f>
-        <v>l-mon-whtap03-nic</v>
-      </c>
-      <c r="V73" s="107" t="b">
-        <v>1</v>
-      </c>
-      <c r="W73" s="107" t="b">
-        <v>1</v>
-      </c>
-      <c r="X73" s="107" t="s">
-        <v>561</v>
-      </c>
-      <c r="Y73" s="107" t="s">
-        <v>259</v>
-      </c>
-      <c r="Z73" s="107" t="s">
-        <v>558</v>
-      </c>
-      <c r="AA73" s="107" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB73" s="107" t="s">
-        <v>561</v>
-      </c>
-      <c r="AC73" s="107" t="s">
-        <v>566</v>
-      </c>
-      <c r="AD73" s="107">
-        <v>3</v>
-      </c>
-      <c r="AE73" s="107"/>
-      <c r="AF73" s="107"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -22628,7 +21788,7 @@
         <v>24</v>
       </c>
       <c r="F71" s="74" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="G71" s="74" t="str">
         <f t="shared" si="2"/>
@@ -22657,10 +21817,10 @@
         <v>196</v>
       </c>
       <c r="O71" s="74" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="P71" s="74" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="Q71" s="74" t="b">
         <v>1</v>
@@ -22672,7 +21832,7 @@
         <v>23</v>
       </c>
       <c r="C72" s="73" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="D72" s="88" t="s">
         <v>553</v>
@@ -22681,7 +21841,7 @@
         <v>24</v>
       </c>
       <c r="F72" s="73" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="G72" s="73" t="str">
         <f t="shared" ref="G72" si="4">SUBSTITUTE($F72,"hazr-","")&amp;"-disk01"</f>
@@ -22710,10 +21870,10 @@
         <v>196</v>
       </c>
       <c r="O72" s="73" t="s">
+        <v>557</v>
+      </c>
+      <c r="P72" s="73" t="s">
         <v>561</v>
-      </c>
-      <c r="P72" s="73" t="s">
-        <v>565</v>
       </c>
       <c r="Q72" s="73" t="b">
         <v>1</v>
@@ -22735,7 +21895,7 @@
         <v>24</v>
       </c>
       <c r="F73" s="74" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="G73" s="74" t="str">
         <f>SUBSTITUTE($F73,"hazr-","")&amp;"-disk01"</f>
@@ -22763,10 +21923,10 @@
         <v>196</v>
       </c>
       <c r="O73" s="74" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="P73" s="74" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="Q73" s="74" t="b">
         <v>1</v>
@@ -26187,7 +25347,7 @@
       <c r="M88" s="73"/>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A89" s="110"/>
+      <c r="A89" s="107"/>
       <c r="B89" s="82" t="s">
         <v>23</v>
       </c>
@@ -26209,26 +25369,26 @@
         <v>259</v>
       </c>
       <c r="H89" s="74" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="I89" s="74" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="J89" s="74" t="s">
         <v>553</v>
       </c>
       <c r="K89" s="74" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="L89" s="74" t="s">
         <v>545</v>
       </c>
       <c r="M89" s="74" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A90" s="110"/>
+      <c r="A90" s="107"/>
       <c r="B90" s="80" t="s">
         <v>23</v>
       </c>
@@ -26250,26 +25410,26 @@
         <v>259</v>
       </c>
       <c r="H90" s="73" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="I90" s="73" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="J90" s="73" t="s">
         <v>553</v>
       </c>
       <c r="K90" s="73" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="L90" s="73" t="s">
         <v>545</v>
       </c>
       <c r="M90" s="73" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A91" s="110"/>
+      <c r="A91" s="107"/>
       <c r="B91" s="82" t="s">
         <v>23</v>
       </c>
@@ -26291,22 +25451,22 @@
         <v>259</v>
       </c>
       <c r="H91" s="74" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="I91" s="74" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="J91" s="74" t="s">
         <v>553</v>
       </c>
       <c r="K91" s="74" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="L91" s="74" t="s">
         <v>545</v>
       </c>
       <c r="M91" s="74" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
     </row>
   </sheetData>
@@ -31866,7 +31026,7 @@
         <v>8080</v>
       </c>
       <c r="I14" s="86" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="J14" s="86">
         <v>5</v>
@@ -32507,7 +31667,7 @@
         <v>8080</v>
       </c>
       <c r="I34" s="86" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="J34" s="86">
         <v>5</v>
@@ -32542,7 +31702,7 @@
         <v>8080</v>
       </c>
       <c r="I35" s="84" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="J35" s="84">
         <v>5</v>
@@ -32744,7 +31904,7 @@
         <v>8080</v>
       </c>
       <c r="I41" s="74" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="J41" s="74">
         <v>5</v>
@@ -32812,7 +31972,7 @@
         <v>20030</v>
       </c>
       <c r="I43" s="74" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="J43" s="74">
         <v>5</v>
@@ -32847,7 +32007,7 @@
         <v>20000</v>
       </c>
       <c r="I44" s="84" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="J44" s="84">
         <v>5</v>
@@ -32882,7 +32042,7 @@
         <v>21000</v>
       </c>
       <c r="I45" s="84" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="J45" s="84">
         <v>5</v>
@@ -32917,7 +32077,7 @@
         <v>22000</v>
       </c>
       <c r="I46" s="84" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="J46" s="84">
         <v>5</v>
@@ -33016,7 +32176,7 @@
         <v>443</v>
       </c>
       <c r="I49" s="74" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="J49" s="74">
         <v>5</v>
@@ -33051,7 +32211,7 @@
         <v>9100</v>
       </c>
       <c r="I50" s="74" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="J50" s="74">
         <v>5</v>
@@ -33086,7 +32246,7 @@
         <v>8883</v>
       </c>
       <c r="I51" s="84" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="J51" s="84">
         <v>5</v>
@@ -33121,7 +32281,7 @@
         <v>1884</v>
       </c>
       <c r="I52" s="84" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="J52" s="84">
         <v>5</v>
@@ -33156,7 +32316,7 @@
         <v>9100</v>
       </c>
       <c r="I53" s="84" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="J53" s="84">
         <v>5</v>
@@ -33191,7 +32351,7 @@
         <v>1883</v>
       </c>
       <c r="I54" s="74" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="J54" s="74">
         <v>5</v>
@@ -33226,7 +32386,7 @@
         <v>1884</v>
       </c>
       <c r="I55" s="74" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="J55" s="74">
         <v>5</v>
@@ -33261,7 +32421,7 @@
         <v>18083</v>
       </c>
       <c r="I56" s="74" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="J56" s="74">
         <v>5</v>
@@ -33296,7 +32456,7 @@
         <v>9100</v>
       </c>
       <c r="I57" s="74" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="J57" s="74">
         <v>5</v>
@@ -33331,7 +32491,7 @@
         <v>3660</v>
       </c>
       <c r="I58" s="84" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="J58" s="84">
         <v>5</v>
@@ -33366,7 +32526,7 @@
         <v>3661</v>
       </c>
       <c r="I59" s="84" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="J59" s="84">
         <v>5</v>
@@ -33401,7 +32561,7 @@
         <v>3670</v>
       </c>
       <c r="I60" s="84" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="J60" s="84">
         <v>5</v>
@@ -33436,7 +32596,7 @@
         <v>3671</v>
       </c>
       <c r="I61" s="84" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="J61" s="84">
         <v>5</v>
@@ -33471,7 +32631,7 @@
         <v>9100</v>
       </c>
       <c r="I62" s="84" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="J62" s="84">
         <v>5</v>
@@ -33506,7 +32666,7 @@
         <v>443</v>
       </c>
       <c r="I63" s="74" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="J63" s="74">
         <v>5</v>
@@ -33541,7 +32701,7 @@
         <v>8100</v>
       </c>
       <c r="I64" s="74" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="J64" s="74">
         <v>5</v>
@@ -33576,7 +32736,7 @@
         <v>8200</v>
       </c>
       <c r="I65" s="74" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="J65" s="74">
         <v>5</v>
@@ -33611,7 +32771,7 @@
         <v>8300</v>
       </c>
       <c r="I66" s="74" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="J66" s="74">
         <v>5</v>
@@ -33646,7 +32806,7 @@
         <v>8400</v>
       </c>
       <c r="I67" s="74" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="J67" s="74">
         <v>5</v>
@@ -33681,7 +32841,7 @@
         <v>9100</v>
       </c>
       <c r="I68" s="74" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="J68" s="74">
         <v>5</v>
@@ -33716,7 +32876,7 @@
         <v>9113</v>
       </c>
       <c r="I69" s="74" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="J69" s="74">
         <v>5</v>
@@ -33751,7 +32911,7 @@
         <v>443</v>
       </c>
       <c r="I70" s="84" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="J70" s="84">
         <v>5</v>
@@ -33786,7 +32946,7 @@
         <v>8085</v>
       </c>
       <c r="I71" s="84" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="J71" s="84">
         <v>5</v>
@@ -33821,7 +32981,7 @@
         <v>8900</v>
       </c>
       <c r="I72" s="84" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="J72" s="84">
         <v>5</v>
@@ -33856,7 +33016,7 @@
         <v>8901</v>
       </c>
       <c r="I73" s="84" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="J73" s="84">
         <v>5</v>
@@ -33891,7 +33051,7 @@
         <v>9100</v>
       </c>
       <c r="I74" s="84" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="J74" s="84">
         <v>5</v>
@@ -34010,7 +33170,7 @@
         <v>443</v>
       </c>
       <c r="I78" s="84" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="J78" s="84">
         <v>5</v>
@@ -34045,7 +33205,7 @@
         <v>8080</v>
       </c>
       <c r="I79" s="84" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="J79" s="84">
         <v>5</v>
@@ -34080,7 +33240,7 @@
         <v>8088</v>
       </c>
       <c r="I80" s="74" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="J80" s="74">
         <v>5</v>
@@ -34115,7 +33275,7 @@
         <v>9003</v>
       </c>
       <c r="I81" s="74" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="J81" s="74">
         <v>5</v>
@@ -34150,7 +33310,7 @@
         <v>9005</v>
       </c>
       <c r="I82" s="74" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="J82" s="74">
         <v>5</v>
@@ -34185,7 +33345,7 @@
         <v>443</v>
       </c>
       <c r="I83" s="84" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="J83" s="84">
         <v>5</v>
@@ -34220,7 +33380,7 @@
         <v>443</v>
       </c>
       <c r="I84" s="74" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="J84" s="74">
         <v>5</v>
@@ -34332,12 +33492,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -34485,15 +33642,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -34517,17 +33685,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>